--- a/workbooks/Trykkberegning_ror.xlsx
+++ b/workbooks/Trykkberegning_ror.xlsx
@@ -14,39 +14,43 @@
     <sheet name="Rørstrekk" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Bend" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Ventiler" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Komponenter" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Ventilkatalog" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Veiledning" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Rørdata" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Materialer" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Medier" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="Beregning" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="_Lister" sheetId="14" state="hidden" r:id="rId16"/>
+    <sheet name="Ventildata" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Komponenter" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Ventilkatalog" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Veiledning" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Rørdata" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Materialer" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Medier" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Beregning" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="_Lister" sheetId="15" state="hidden" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Bend!$A$1:$L$36</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Bend!$A$6:$K$31</definedName>
-    <definedName function="false" hidden="false" localSheetId="12" name="_xlnm.Print_Area" vbProcedure="false">Beregning!$A$1:$E$40</definedName>
-    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">Komponenter!$A$1:$F$36</definedName>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Komponenter!$A$6:$F$31</definedName>
-    <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Area" vbProcedure="false">Materialer!$A$1:$E$20</definedName>
-    <definedName function="false" hidden="false" localSheetId="11" name="_xlnm.Print_Area" vbProcedure="false">Medier!$A$1:$D$18</definedName>
+    <definedName function="false" hidden="false" localSheetId="13" name="_xlnm.Print_Area" vbProcedure="false">Beregning!$A$1:$E$40</definedName>
+    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">Komponenter!$A$1:$F$36</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Komponenter!$A$6:$F$31</definedName>
+    <definedName function="false" hidden="false" localSheetId="11" name="_xlnm.Print_Area" vbProcedure="false">Materialer!$A$1:$E$20</definedName>
+    <definedName function="false" hidden="false" localSheetId="12" name="_xlnm.Print_Area" vbProcedure="false">Medier!$A$1:$D$18</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Reduksjoner!$A$1:$L$37</definedName>
-    <definedName function="false" hidden="false" localSheetId="9" name="_xlnm.Print_Area" vbProcedure="false">Rørdata!$B$1:$E$52</definedName>
-    <definedName function="false" hidden="false" localSheetId="9" name="_xlnm.Print_Titles" vbProcedure="false">Rørdata!$1:$6</definedName>
-    <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">Rørdata!$A$6:$E$52</definedName>
+    <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Area" vbProcedure="false">Rørdata!$B$1:$E$52</definedName>
+    <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Titles" vbProcedure="false">Rørdata!$1:$6</definedName>
+    <definedName function="false" hidden="true" localSheetId="10" name="_xlnm._FilterDatabase" vbProcedure="false">Rørdata!$A$6:$E$52</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Rørstrekk!$A$1:$J$37</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Rørstyrke!$A$1:$M$39</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Trykkberegning!$A$1:$N$45</definedName>
-    <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Area" vbProcedure="false">Veiledning!$A$1:$C$23</definedName>
-    <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Titles" vbProcedure="false">Veiledning!$1:$3</definedName>
-    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Ventiler!$A$1:$M$36</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Ventiler!$A$6:$F$31</definedName>
-    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">Ventilkatalog!$A$1:$E$12</definedName>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Ventilkatalog!$A$6:$E$12</definedName>
+    <definedName function="false" hidden="false" localSheetId="9" name="_xlnm.Print_Area" vbProcedure="false">Veiledning!$A$1:$C$23</definedName>
+    <definedName function="false" hidden="false" localSheetId="9" name="_xlnm.Print_Titles" vbProcedure="false">Veiledning!$1:$3</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">Ventildata!$A$1:$J$54</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Ventildata!$A$6:$J$48</definedName>
+    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Ventiler!$A$1:$R$36</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Ventiler!$A$6:$R$31</definedName>
+    <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Area" vbProcedure="false">Ventilkatalog!$A$1:$E$15</definedName>
+    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">Ventilkatalog!$A$6:$E$15</definedName>
     <definedName function="false" hidden="false" name="Benddata" vbProcedure="false">_Lister!$I$2:$K$8</definedName>
     <definedName function="false" hidden="false" name="Bendtyper" vbProcedure="false">_Lister!$G$2:$G$8</definedName>
     <definedName function="false" hidden="false" name="ENStandarder" vbProcedure="false">_Lister!$E$2:$E$9</definedName>
+    <definedName function="false" hidden="false" name="GenerelleVentildata" vbProcedure="false">Ventildata!$A$7:$J$48</definedName>
     <definedName function="false" hidden="false" name="Materialdata" vbProcedure="false">Materialer!$A$7:$E$12</definedName>
     <definedName function="false" hidden="false" name="Materialvalg" vbProcedure="false">_Lister!$D$2:$D$7</definedName>
     <definedName function="false" hidden="false" name="Mediedata" vbProcedure="false">Medier!$A$7:$D$13</definedName>
@@ -55,8 +59,8 @@
     <definedName function="false" hidden="false" name="NominelleDN" vbProcedure="false">_Lister!$B$2:$B$16</definedName>
     <definedName function="false" hidden="false" name="Roroppslag" vbProcedure="false">Rørdata!$A$7:$E$52</definedName>
     <definedName function="false" hidden="false" name="Rorserier" vbProcedure="false">_Lister!$A$2:$A$4</definedName>
-    <definedName function="false" hidden="false" name="Ventiloppslag" vbProcedure="false">Ventilkatalog!$A$7:$E$12</definedName>
-    <definedName function="false" hidden="false" name="Ventilvalg" vbProcedure="false">Ventilkatalog!$A$7:$A$12</definedName>
+    <definedName function="false" hidden="false" name="Ventiloppslag" vbProcedure="false">Ventilkatalog!$A$7:$E$15</definedName>
+    <definedName function="false" hidden="false" name="Ventilvalg" vbProcedure="false">Ventilkatalog!$A$7:$A$15</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -709,8 +713,618 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>R-rdimensjonering</author>
+  </authors>
+  <commentList>
+    <comment ref="N7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eget K referert til hastighet ved ID brukt. Dokumenter kilde i kommentar. Kan også brukes ved andre åpninger/strømningsregimer når K gjelder disse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tomt = hoved-ID. Etter reduksjon oppgis aktuell ID som finnes i Reduksjoner. DN i G velges separat; DN er nominelt, ikke ventilens borediameter.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="493">
   <si>
     <t xml:space="preserve">TRYKKBEREGNING AV RØR</t>
   </si>
@@ -910,7 +1524,7 @@
     <t xml:space="preserve">Styrkeberegning og sikkerhetsfaktor →</t>
   </si>
   <si>
-    <t xml:space="preserve">Fagerberg: katalog og datakilder →</t>
+    <t xml:space="preserve">Generelle ventiler: K, Kv og datakilder →</t>
   </si>
   <si>
     <t xml:space="preserve">RØRSTYRKE – INDRE OVERTRYKK</t>
@@ -1201,10 +1815,10 @@
     <t xml:space="preserve">Trykkfall skal være oppgitt ved volumstrømmen og driftsbetingelsene i hovedfanen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Velg modell, antall og dokumentert Δp per enhet. Alternativt oppgis faktisk Kv, DN og åpning; kv-beregning må bekreftes for valgt væske.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eget Δp i kPa overstyrer Kv. Kv: Δp [kPa] = 100 · (ρ/1000) · (Q [m³/h]/Kv)². Ingen automatisk viskositets- eller kavitasjonskorreksjon.</t>
+    <t xml:space="preserve">Generell ventil + antall gir automatisk trykktap. DN følger hovedfanen; bruk lokal ID etter reduksjon. Estimatene gjelder helt åpen ventil og turbulent strømning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prioritet: eget Δp → dokumentert Kv → eget K → generell K-modell. K og ekvivalent Kv vises. Skyvespjeld er et sluseanslag; ingen verifisert leverandørgjennomsnitt eller åpningstilpasning.</t>
   </si>
   <si>
     <t xml:space="preserve">Ventil / komponent</t>
@@ -1213,7 +1827,7 @@
     <t xml:space="preserve">DN / størrelse</t>
   </si>
   <si>
-    <t xml:space="preserve">Dokumentert Kv [m³/h]</t>
+    <t xml:space="preserve">Eget dokumentert Kv [m³/h]</t>
   </si>
   <si>
     <t xml:space="preserve">Åpning [%]</t>
@@ -1225,88 +1839,343 @@
     <t xml:space="preserve">Produktlenke</t>
   </si>
   <si>
-    <t xml:space="preserve">Kv-modell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kv verifisert?</t>
+    <t xml:space="preserve">Metode / estimatgrunnlag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eget Kv verifisert?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K brukt, lokal ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID brukt [mm]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kv ekv. fra K [m³/h]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spjeldventil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sluseventil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUM TRYKKTAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrer hver fysisk komponent én gang. En ventil som er lagt inn med trykkfall her, skal ikke i tillegg registreres som K-motstand i Bend-fanen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENERELLE VENTILER – K OG EKVIVALENT Kv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full åpning · modellestimater · DN15–300 · faktisk lokal ID brukes i ventilberegningen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingen verifisert snittverdi fra flere leverandører. Crane-referanser gjengitt i fluids; skyvespjeld bruker et uttrykkelig sluseanslag. Referanse-ID i denne tabellen = DN i mm, ikke produsentens ventilboring. Små spjeld utenfor modellområdet har ingen verdi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oppslagsnøkkel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ventilvalg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referanse-ID [mm]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N i K=N·fT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fT referanse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K referanse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kv ekv. [m³/h]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grunnlag / gyldighet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crane: K=3 fT, full lysåpning og helt åpen kule. Ingen redusert boring.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raw.githubusercontent.com/CalebBell/fluids/master/fluids/fittings.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generell kuleventil – full åpning|DN300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DN300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utenfor modellområde: bruk dokumentert Kv eller eget K.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anslag K=8 fT fra Crane sluseventil. Ikke en dokumentert skyvespjeldskorrelasjon; bare full åpning, fri passasje og klar væske.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt skyvespjeld – sluseanslag|DN300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crane sentrisk dreiespjeld, helt åpent: K=45 fT for DN50–200, 35 fT for DN250–300. Gjelder ikke eksentriske spjeld.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelt dreiespjeld – sentrisk|DN300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Δp = K·ρ·v²/2. K er dimensjonsløs og refererer til faktisk lokal rør-ID. Ekvivalent Kv = 3600·A·√(200/K), med A i m². fT: Colebrook med Re*=7,5·10⁶·D og ε/D=3,4126825352925·10⁻⁵·D^(−1,0112), D i meter (fluids-tilpasning til Crane). Dette er ikke rørets friksjonsfaktor. Generell modell brukes bare ved Re≥4000 eller null strømning, og 100 % åpning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde innhentet 2026-10-14: https://raw.githubusercontent.com/CalebBell/fluids/master/fluids/friction.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRE KOMPONENTER – TRYKKFALL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fyll inn antall og trykkfall PER ENHET i kPa. 1 bar = 100 kPa. Trykkfallene summeres som antall × Δp per enhet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verdiene skaleres ikke automatisk når volumstrømmen endres. Oppdater dem fra leverandørdata. Antall 0 utelater raden.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varmeveksler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mengdemåler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annen komponent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VENTILKATALOG – GENERELLE MODELLER OG EGNE DATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generelle K-estimater finnes i Ventildata. Egen Δp, Kv eller K kan overstyre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 generelle ventilmodeller tilgjengelige. Modellgrunnlag: Crane via fluids; ikke verifisert snitt fra flere leverandører. Fagerberg-produktdata: 0 importerte produkter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valg i ventilfanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kategori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produsent / modell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde-URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hentedato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egen ventil (dokumentert)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egen</t>
   </si>
   <si>
     <t xml:space="preserve">Kuleventil</t>
   </si>
   <si>
+    <t xml:space="preserve">Generisk</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reguleringsventil</t>
   </si>
   <si>
     <t xml:space="preserve">Tilbakeslagsventil</t>
   </si>
   <si>
-    <t xml:space="preserve">Spjeldventil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sluseventil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUM TRYKKTAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registrer hver fysisk komponent én gang. En ventil som er lagt inn med trykkfall her, skal ikke i tillegg registreres som K-motstand i Bend-fanen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANDRE KOMPONENTER – TRYKKFALL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fyll inn antall og trykkfall PER ENHET i kPa. 1 bar = 100 kPa. Trykkfallene summeres som antall × Δp per enhet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verdiene skaleres ikke automatisk når volumstrømmen endres. Oppdater dem fra leverandørdata. Antall 0 utelater raden.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varmeveksler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mengdemåler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annen komponent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAGERBERG NORGE – VENTILKATALOG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produktvalg og kilder. Kv og trykkfall må dokumenteres for aktuell DN, åpning og væske.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KATALOG IKKE INNHENTET – nettsiden er blokkert av miljøets nettverksregler. Ingen Fagerberg-modeller er oppdiktet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valg i ventilfanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kategori</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produsent / modell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilde-URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hentedato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egen ventil (dokumentert)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generisk</t>
+    <t xml:space="preserve">Modellestimat, ikke leverandørprodukt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyvespjeldsventil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dreiespjeldsventil</t>
   </si>
   <si>
     <t xml:space="preserve">SLIK BRUKER DU ARKET</t>
@@ -1381,10 +2250,10 @@
     <t xml:space="preserve">Oppgi reduksjoner/ekspansjoner i rekkefølge, én per aktiv rad, med faktisk ID før/etter og aksial lengde. K refererer til liten diameter. Lokalt tap = Kρvliten²/2; hastighetsbidrag beregnes én gang ved endene. Crane: reduksjon K=0,8 sin(θ/2)(1−β²) ved θ&lt;45°, ellers 0,5√sin(θ/2)(1−β²). Ekspansjon K=2,6 sin(θ/2)(1−β²)² ved θ&lt;45°, ellers (1−β²)². β=Dliten/Dstor; θ full konusvinkel. Eget K overstyrer. Kilder: Crane TP410 og fluids.fittings.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ventilkatalog og Kv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velg modell fra Ventilkatalog. Katalogen viser faktisk importstatus og kilde-URL, og inneholder ingen oppdiktede leverandørmodeller. Δp per ventil kan oppgis direkte. Alternativt brukes dokumentert Kv ved angitt DN og åpning: Δp[kPa]=100(ρ/1000)(Q/Kv)². Kv-metoden må bekreftes for væske/viskositet og åpning; ingen automatisk korreksjon for laminar strømning, kavitasjon eller choking.</t>
+    <t xml:space="preserve">Ventilkatalog, K og Kv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velg en generell kuleventil, skyvespjeld eller sentrisk dreiespjeld for automatisk trykktap ved 100 % åpning og Re&gt;=4000. DN følger hovedfanen og faktisk ID brukes; etter reduksjon velges DN og lokal ID på raden. Ventildata viser K, ekvivalent Kv og referanser. Crane-estimater er ikke et verifisert leverandørsnitt; skyvespjeld bruker uttrykkelig et sluseanslag. Prioritet: eget Δp, dokumentert Kv, eget K, generell modell. Δp[kPa]=Kρv²/2000 eller 100(ρ/1000)(Q/Kv)². Eget K trenger kilde; eget Kv må bekreftes ved aktuell DN, åpning og væske. Ingen automatisk viskositets-, kavitasjons- eller chokingkorreksjon.</t>
   </si>
   <si>
     <t xml:space="preserve">Darcy–Weisbach / Colebrook</t>
@@ -1414,9 +2283,6 @@
     <t xml:space="preserve">Utvalg vanlige ytre diametre. DN er nominelt; innvendig diameter krever veggtykkelse eller egen verdi.</t>
   </si>
   <si>
-    <t xml:space="preserve">Oppslagsnøkkel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rørserie</t>
   </si>
   <si>
@@ -1432,85 +2298,46 @@
     <t xml:space="preserve">EN 10220 / ISO 4200|DN15</t>
   </si>
   <si>
-    <t xml:space="preserve">DN15</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vanlig OD-utvalg, ikke komplett normtabell. Kontroller mot rørsertifikat og aktuell normutgave.</t>
   </si>
   <si>
     <t xml:space="preserve">EN 10220 / ISO 4200|DN20</t>
   </si>
   <si>
-    <t xml:space="preserve">DN20</t>
-  </si>
-  <si>
     <t xml:space="preserve">EN 10220 / ISO 4200|DN25</t>
   </si>
   <si>
-    <t xml:space="preserve">DN25</t>
-  </si>
-  <si>
     <t xml:space="preserve">EN 10220 / ISO 4200|DN32</t>
   </si>
   <si>
-    <t xml:space="preserve">DN32</t>
-  </si>
-  <si>
     <t xml:space="preserve">EN 10220 / ISO 4200|DN40</t>
   </si>
   <si>
-    <t xml:space="preserve">DN40</t>
-  </si>
-  <si>
     <t xml:space="preserve">EN 10220 / ISO 4200|DN50</t>
   </si>
   <si>
-    <t xml:space="preserve">DN50</t>
-  </si>
-  <si>
     <t xml:space="preserve">EN 10220 / ISO 4200|DN65</t>
   </si>
   <si>
-    <t xml:space="preserve">DN65</t>
-  </si>
-  <si>
     <t xml:space="preserve">EN 10220 / ISO 4200|DN80</t>
   </si>
   <si>
     <t xml:space="preserve">EN 10220 / ISO 4200|DN100</t>
   </si>
   <si>
-    <t xml:space="preserve">DN100</t>
-  </si>
-  <si>
     <t xml:space="preserve">EN 10220 / ISO 4200|DN125</t>
   </si>
   <si>
-    <t xml:space="preserve">DN125</t>
-  </si>
-  <si>
     <t xml:space="preserve">EN 10220 / ISO 4200|DN150</t>
   </si>
   <si>
-    <t xml:space="preserve">DN150</t>
-  </si>
-  <si>
     <t xml:space="preserve">EN 10220 / ISO 4200|DN200</t>
   </si>
   <si>
-    <t xml:space="preserve">DN200</t>
-  </si>
-  <si>
     <t xml:space="preserve">EN 10220 / ISO 4200|DN250</t>
   </si>
   <si>
-    <t xml:space="preserve">DN250</t>
-  </si>
-  <si>
     <t xml:space="preserve">EN 10220 / ISO 4200|DN300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DN300</t>
   </si>
   <si>
     <t xml:space="preserve">ISO 1127|DN15</t>
@@ -2246,7 +3073,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2414,6 +3241,10 @@
     <xf numFmtId="181" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
@@ -2714,11 +3545,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="33228727"/>
-        <c:axId val="45193834"/>
+        <c:axId val="40265228"/>
+        <c:axId val="18211899"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="33228727"/>
+        <c:axId val="40265228"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2751,14 +3582,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45193834"/>
+        <c:crossAx val="18211899"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45193834"/>
+        <c:axId val="18211899"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2834,7 +3665,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33228727"/>
+        <c:crossAx val="40265228"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3134,6 +3965,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -4208,7 +5043,7 @@
     <hyperlink ref="A42" r:id="rId5" location="'Reduksjoner'!A1" display="Reduksjoner og endehastighet →"/>
     <hyperlink ref="A43" r:id="rId6" location="'Rørstrekk'!A1" display="Rette rør med flere diametre →"/>
     <hyperlink ref="A44" r:id="rId7" location="'Rørstyrke'!A1" display="Styrkeberegning og sikkerhetsfaktor →"/>
-    <hyperlink ref="A45" r:id="rId8" location="'Ventilkatalog'!A1" display="Fagerberg: katalog og datakilder →"/>
+    <hyperlink ref="A45" r:id="rId8" location="'Ventildata'!A1" display="Generelle ventiler: K, Kv og datakilder →"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.15"/>
@@ -4228,6 +5063,262 @@
     <tabColor rgb="FF087F8C"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
+  <dimension ref="A1:C54"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="115"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="129.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C23" s="43" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="A3:C3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C23" r:id="rId1" display="Dokumentert referanseimplementasjon: fluids / fittings.py"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.15"/>
+  <pageSetup paperSize="8" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 R-rdimensjonering | &amp;A | side &amp;P av &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF087F8C"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1:E54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -4240,7 +5331,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>317</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4256,7 +5347,7 @@
     </row>
     <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>233</v>
+        <v>318</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -4267,143 +5358,143 @@
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>234</v>
+        <v>186</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>235</v>
+        <v>319</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>236</v>
+        <v>320</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>237</v>
+        <v>321</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>238</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>239</v>
+        <v>323</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="D7" s="43" t="n">
+        <v>197</v>
+      </c>
+      <c r="D7" s="44" t="n">
         <v>21.3</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>242</v>
+        <v>325</v>
       </c>
       <c r="B8" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="D8" s="43" t="n">
+        <v>201</v>
+      </c>
+      <c r="D8" s="44" t="n">
         <v>26.9</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>244</v>
+        <v>326</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="D9" s="43" t="n">
+        <v>203</v>
+      </c>
+      <c r="D9" s="44" t="n">
         <v>33.7</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>246</v>
+        <v>327</v>
       </c>
       <c r="B10" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>247</v>
-      </c>
-      <c r="D10" s="43" t="n">
+        <v>205</v>
+      </c>
+      <c r="D10" s="44" t="n">
         <v>42.4</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>248</v>
+        <v>328</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>249</v>
-      </c>
-      <c r="D11" s="43" t="n">
+        <v>207</v>
+      </c>
+      <c r="D11" s="44" t="n">
         <v>48.3</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="B12" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="D12" s="43" t="n">
+        <v>209</v>
+      </c>
+      <c r="D12" s="44" t="n">
         <v>60.3</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>252</v>
+        <v>330</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="D13" s="43" t="n">
+        <v>211</v>
+      </c>
+      <c r="D13" s="44" t="n">
         <v>76.1</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>254</v>
+        <v>331</v>
       </c>
       <c r="B14" s="27" t="s">
         <v>5</v>
@@ -4411,657 +5502,657 @@
       <c r="C14" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="43" t="n">
+      <c r="D14" s="44" t="n">
         <v>88.9</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>255</v>
+        <v>332</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="D15" s="43" t="n">
+        <v>214</v>
+      </c>
+      <c r="D15" s="44" t="n">
         <v>114.3</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
-        <v>257</v>
+        <v>333</v>
       </c>
       <c r="B16" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="D16" s="43" t="n">
+        <v>216</v>
+      </c>
+      <c r="D16" s="44" t="n">
         <v>139.7</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>259</v>
+        <v>334</v>
       </c>
       <c r="B17" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="D17" s="43" t="n">
+        <v>218</v>
+      </c>
+      <c r="D17" s="44" t="n">
         <v>168.3</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>261</v>
+        <v>335</v>
       </c>
       <c r="B18" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="D18" s="43" t="n">
+        <v>220</v>
+      </c>
+      <c r="D18" s="44" t="n">
         <v>219.1</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>263</v>
+        <v>336</v>
       </c>
       <c r="B19" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="D19" s="43" t="n">
+        <v>222</v>
+      </c>
+      <c r="D19" s="44" t="n">
         <v>273</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
-        <v>265</v>
+        <v>337</v>
       </c>
       <c r="B20" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>266</v>
-      </c>
-      <c r="D20" s="43" t="n">
+        <v>224</v>
+      </c>
+      <c r="D20" s="44" t="n">
         <v>323.9</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>267</v>
+        <v>338</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="D21" s="43" t="n">
+        <v>197</v>
+      </c>
+      <c r="D21" s="44" t="n">
         <v>21.3</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>269</v>
+        <v>340</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="D22" s="43" t="n">
+        <v>201</v>
+      </c>
+      <c r="D22" s="44" t="n">
         <v>26.9</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>270</v>
+        <v>341</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="D23" s="43" t="n">
+        <v>203</v>
+      </c>
+      <c r="D23" s="44" t="n">
         <v>33.7</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>271</v>
+        <v>342</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>247</v>
-      </c>
-      <c r="D24" s="43" t="n">
+        <v>205</v>
+      </c>
+      <c r="D24" s="44" t="n">
         <v>42.4</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>272</v>
+        <v>343</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>249</v>
-      </c>
-      <c r="D25" s="43" t="n">
+        <v>207</v>
+      </c>
+      <c r="D25" s="44" t="n">
         <v>48.3</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>273</v>
+        <v>344</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="D26" s="43" t="n">
+        <v>209</v>
+      </c>
+      <c r="D26" s="44" t="n">
         <v>60.3</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>274</v>
+        <v>345</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="D27" s="43" t="n">
+        <v>211</v>
+      </c>
+      <c r="D27" s="44" t="n">
         <v>76.1</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
-        <v>275</v>
+        <v>346</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C28" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="43" t="n">
+      <c r="D28" s="44" t="n">
         <v>88.9</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>276</v>
+        <v>347</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="D29" s="43" t="n">
+        <v>214</v>
+      </c>
+      <c r="D29" s="44" t="n">
         <v>114.3</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="27" t="s">
-        <v>277</v>
+        <v>348</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="D30" s="43" t="n">
+        <v>216</v>
+      </c>
+      <c r="D30" s="44" t="n">
         <v>139.7</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
-        <v>278</v>
+        <v>349</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="D31" s="43" t="n">
+        <v>218</v>
+      </c>
+      <c r="D31" s="44" t="n">
         <v>168.3</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="27" t="s">
-        <v>279</v>
+        <v>350</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="D32" s="43" t="n">
+        <v>220</v>
+      </c>
+      <c r="D32" s="44" t="n">
         <v>219.1</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>280</v>
+        <v>351</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="D33" s="43" t="n">
+        <v>222</v>
+      </c>
+      <c r="D33" s="44" t="n">
         <v>273</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="27" t="s">
-        <v>281</v>
+        <v>352</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>266</v>
-      </c>
-      <c r="D34" s="43" t="n">
+        <v>224</v>
+      </c>
+      <c r="D34" s="44" t="n">
         <v>323.9</v>
       </c>
       <c r="E34" s="27" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>282</v>
+        <v>353</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="D35" s="43" t="n">
+        <v>355</v>
+      </c>
+      <c r="D35" s="44" t="n">
         <v>20</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="27" t="s">
-        <v>286</v>
+        <v>357</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>287</v>
-      </c>
-      <c r="D36" s="43" t="n">
+        <v>358</v>
+      </c>
+      <c r="D36" s="44" t="n">
         <v>25</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="27" t="s">
-        <v>288</v>
+        <v>359</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>289</v>
-      </c>
-      <c r="D37" s="43" t="n">
+        <v>360</v>
+      </c>
+      <c r="D37" s="44" t="n">
         <v>32</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="27" t="s">
-        <v>290</v>
+        <v>361</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>291</v>
-      </c>
-      <c r="D38" s="43" t="n">
+        <v>362</v>
+      </c>
+      <c r="D38" s="44" t="n">
         <v>40</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="27" t="s">
-        <v>292</v>
+        <v>363</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>293</v>
-      </c>
-      <c r="D39" s="43" t="n">
+        <v>364</v>
+      </c>
+      <c r="D39" s="44" t="n">
         <v>50</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
-        <v>294</v>
+        <v>365</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="D40" s="43" t="n">
+        <v>366</v>
+      </c>
+      <c r="D40" s="44" t="n">
         <v>63</v>
       </c>
       <c r="E40" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>296</v>
+        <v>367</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="D41" s="43" t="n">
+        <v>368</v>
+      </c>
+      <c r="D41" s="44" t="n">
         <v>75</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="27" t="s">
-        <v>298</v>
+        <v>369</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="D42" s="43" t="n">
+        <v>370</v>
+      </c>
+      <c r="D42" s="44" t="n">
         <v>90</v>
       </c>
       <c r="E42" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>300</v>
+        <v>371</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="D43" s="43" t="n">
+        <v>372</v>
+      </c>
+      <c r="D43" s="44" t="n">
         <v>110</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="27" t="s">
-        <v>302</v>
+        <v>373</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>303</v>
-      </c>
-      <c r="D44" s="43" t="n">
+        <v>374</v>
+      </c>
+      <c r="D44" s="44" t="n">
         <v>125</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>304</v>
+        <v>375</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="D45" s="43" t="n">
+        <v>376</v>
+      </c>
+      <c r="D45" s="44" t="n">
         <v>140</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="27" t="s">
-        <v>306</v>
+        <v>377</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="D46" s="43" t="n">
+        <v>378</v>
+      </c>
+      <c r="D46" s="44" t="n">
         <v>160</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>308</v>
+        <v>379</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="D47" s="43" t="n">
+        <v>380</v>
+      </c>
+      <c r="D47" s="44" t="n">
         <v>180</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="27" t="s">
-        <v>310</v>
+        <v>381</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>311</v>
-      </c>
-      <c r="D48" s="43" t="n">
+        <v>382</v>
+      </c>
+      <c r="D48" s="44" t="n">
         <v>200</v>
       </c>
       <c r="E48" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="27" t="s">
-        <v>312</v>
+        <v>383</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="D49" s="43" t="n">
+        <v>384</v>
+      </c>
+      <c r="D49" s="44" t="n">
         <v>225</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="27" t="s">
-        <v>314</v>
+        <v>385</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="D50" s="43" t="n">
+        <v>386</v>
+      </c>
+      <c r="D50" s="44" t="n">
         <v>250</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>316</v>
+        <v>387</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="D51" s="43" t="n">
+        <v>388</v>
+      </c>
+      <c r="D51" s="44" t="n">
         <v>280</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="27" t="s">
-        <v>318</v>
+        <v>389</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>319</v>
-      </c>
-      <c r="D52" s="43" t="n">
+        <v>390</v>
+      </c>
+      <c r="D52" s="44" t="n">
         <v>315</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5083,7 +6174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF087F8C"/>
@@ -5101,7 +6192,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>391</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5117,7 +6208,7 @@
     </row>
     <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>321</v>
+        <v>392</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -5128,16 +6219,16 @@
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>322</v>
+        <v>393</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>323</v>
+        <v>394</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>324</v>
+        <v>395</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>325</v>
+        <v>396</v>
       </c>
       <c r="E6" s="27" t="s">
         <v>112</v>
@@ -5148,125 +6239,125 @@
         <v>18</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>326</v>
+        <v>397</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>0.045</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>327</v>
+        <v>398</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>328</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>329</v>
+        <v>400</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>330</v>
+        <v>401</v>
       </c>
       <c r="C8" s="14" t="n">
         <v>0.045</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>327</v>
+        <v>398</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>328</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>331</v>
+        <v>402</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>332</v>
+        <v>403</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>0.045</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>333</v>
+        <v>404</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>334</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>335</v>
+        <v>406</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>336</v>
+        <v>407</v>
       </c>
       <c r="C10" s="14" t="n">
         <v>0.015</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>337</v>
+        <v>408</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>338</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>339</v>
+        <v>410</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>340</v>
+        <v>411</v>
       </c>
       <c r="C11" s="14" t="n">
         <v>0.015</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>337</v>
+        <v>408</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>338</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>341</v>
+        <v>412</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>342</v>
+        <v>413</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>0.015</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>337</v>
+        <v>408</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>343</v>
+        <v>414</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="44" t="s">
-        <v>344</v>
-      </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
+      <c r="A15" s="45" t="s">
+        <v>415</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
     </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="44"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
+      <c r="A16" s="45"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
     </row>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>345</v>
+        <v>416</v>
       </c>
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
@@ -5332,7 +6423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF087F8C"/>
@@ -5349,7 +6440,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>417</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5363,7 +6454,7 @@
     </row>
     <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>347</v>
+        <v>418</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -5373,21 +6464,21 @@
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>348</v>
+        <v>419</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>349</v>
+        <v>420</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>350</v>
+        <v>421</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>351</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>352</v>
+        <v>423</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>999.97</v>
@@ -5396,7 +6487,7 @@
         <v>1.519</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>353</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5410,12 +6501,12 @@
         <v>1.002</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>353</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>354</v>
+        <v>425</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>992.2</v>
@@ -5424,12 +6515,12 @@
         <v>0.653</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>353</v>
+        <v>424</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>355</v>
+        <v>426</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>983.2</v>
@@ -5438,12 +6529,12 @@
         <v>0.466</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>353</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>356</v>
+        <v>427</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>971.8</v>
@@ -5452,12 +6543,12 @@
         <v>0.354</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>353</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>357</v>
+        <v>428</v>
       </c>
       <c r="B12" s="14" t="n">
         <v>850</v>
@@ -5466,12 +6557,12 @@
         <v>27.2</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>358</v>
+        <v>429</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>359</v>
+        <v>430</v>
       </c>
       <c r="B13" s="14" t="n">
         <v>0</v>
@@ -5480,24 +6571,24 @@
         <v>0</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>360</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="44" t="s">
-        <v>361</v>
-      </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
+      <c r="A16" s="45" t="s">
+        <v>432</v>
+      </c>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
     </row>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="44"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
     </row>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5552,7 +6643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF617589"/>
@@ -5569,24 +6660,24 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="45" t="s">
-        <v>362</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
+      <c r="A1" s="46" t="s">
+        <v>433</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
+      <c r="A2" s="46"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
     </row>
     <row r="3" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
-        <v>363</v>
+        <v>434</v>
       </c>
       <c r="B3" s="27" t="str">
         <f aca="false">IFERROR(IF(COUNTIF(Rorserier,Trykkberegning!E6)=0,"FEIL: velg en gyldig rørserie.",IF(COUNTIF(Materialvalg,Trykkberegning!E13)=0,"FEIL: velg materiale.",IF(COUNTIF(ENStandarder,Trykkberegning!E14)=0,"FEIL: velg EN-produktstandard.",IF(AND(Trykkberegning!E14&lt;&gt;"Annen / dokumentert",ISERROR(SEARCH("|"&amp;Trykkberegning!E14&amp;"|",VLOOKUP(Trykkberegning!E13,Materialdata,4,FALSE())))),"FEIL: EN-produktstandard passer ikke materialvalget. Se Materialer.",IF(COUNTIF(Medievalg,Trykkberegning!E20)=0,"FEIL: velg medium.",IF(OR(NOT(ISNUMBER(Trykkberegning!E21)),Trykkberegning!E21&lt;=0,NOT(ISNUMBER(Trykkberegning!E22)),Trykkberegning!E22&lt;=0),"FEIL: tetthet og dynamisk viskositet må være større enn 0.",IF(OR(NOT(ISNUMBER(Trykkberegning!E12)),Trykkberegning!E12&lt;=0),"FEIL: innvendig diameter må være større enn 0. Kontroller dimensjon og veggtykkelse.",IF(AND(Trykkberegning!E11="",OR(NOT(ISNUMBER(Trykkberegning!E10)),Trykkberegning!E10&lt;=0)),"FEIL: oppgi positiv veggtykkelse eller egen innvendig diameter.",IF(OR(NOT(ISNUMBER(Trykkberegning!E8)),Trykkberegning!E8&lt;0,AND(Trykkberegning!E8&gt;0,Trykkberegning!E12&gt;Trykkberegning!E8)),"FEIL: kontroller ytre og indre diameter.",IF(OR(NOT(ISNUMBER(Trykkberegning!E15)),Trykkberegning!E15&lt;0,Trykkberegning!E15&gt;=Trykkberegning!E12),"FEIL: ruhet må være &gt;=0 og mindre enn innvendig diameter.",IF(OR(Trykkberegning!E17="",NOT(ISNUMBER(Trykkberegning!E17)),Trykkberegning!E17&lt;0,Trykkberegning!E17&lt;&gt;INT(Trykkberegning!E17)),"FEIL: flenskoblinger må være et heltall &gt;=0.",IF(AND(Trykkberegning!E17&gt;0,OR(Trykkberegning!E18="",NOT(ISNUMBER(Trykkberegning!E18)),Trykkberegning!E18&lt;0)),"FEIL: oppgi K &gt;=0 per flenskobling.",IF(OR(Trykkberegning!E25="",NOT(ISNUMBER(Trykkberegning!E25)),Trykkberegning!E25&lt;0),"FEIL: volumstrøm må være et tall &gt;=0.",IF(OR(Trykkberegning!E29="",NOT(ISNUMBER(Trykkberegning!E29)),Trykkberegning!E29&lt;0,Trykkberegning!E30="",NOT(ISNUMBER(Trykkberegning!E30)),Trykkberegning!E30&lt;0,Trykkberegning!E31="",NOT(ISNUMBER(Trykkberegning!E31)),Trykkberegning!E31&lt;0),"FEIL: rette meter og høydemeter må være tall &gt;=0.",IF(AND(Trykkberegning!E33&lt;&gt;"",NOT(ISNUMBER(Trykkberegning!E33))),"FEIL: innløpstrykk må være et tall eller tomt.","OK"))))))))))))))),"FEIL: kontroller inndata; tallfelt kan ikke inneholde tekst.")</f>
@@ -5596,7 +6687,7 @@
     </row>
     <row r="4" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="27" t="s">
-        <v>364</v>
+        <v>435</v>
       </c>
       <c r="B4" s="27" t="str">
         <f aca="false">IFERROR(IF((IFERROR(IF(B3&lt;&gt;"OK",B3,IF(AND(B14&gt;=2300,B14&lt;4000),"FEIL: Reynolds 2300–4000 er overgangsområde; modellen gir ikke et sikkert resultat.",IF(COUNTIF(Bend!J7:J31,"OK")+COUNTIF(Bend!J7:J31,"Ikke med")&lt;&gt;25,"FEIL: kontroller aktive rader i Bend.",IF(COUNTIF(Ventiler!F7:F31,"OK")+COUNTIF(Ventiler!F7:F31,"Ikke med")&lt;&gt;25,"FEIL: kontroller aktive rader i Ventiler.",IF(COUNTIF(Komponenter!F7:F31,"OK")+COUNTIF(Komponenter!F7:F31,"Ikke med")&lt;&gt;25,"FEIL: kontroller aktive rader i Komponenter.",IF(AND(B7=0,SUM(Ventiler!D7:D31,Komponenter!D7:D31)&gt;0),"FEIL: ved null volumstrøm må komponenttrykkfall være 0.","OK")))))),"FEIL: kontroller beregningsformler."))&lt;&gt;"OK",(IFERROR(IF(B3&lt;&gt;"OK",B3,IF(AND(B14&gt;=2300,B14&lt;4000),"FEIL: Reynolds 2300–4000 er overgangsområde; modellen gir ikke et sikkert resultat.",IF(COUNTIF(Bend!J7:J31,"OK")+COUNTIF(Bend!J7:J31,"Ikke med")&lt;&gt;25,"FEIL: kontroller aktive rader i Bend.",IF(COUNTIF(Ventiler!F7:F31,"OK")+COUNTIF(Ventiler!F7:F31,"Ikke med")&lt;&gt;25,"FEIL: kontroller aktive rader i Ventiler.",IF(COUNTIF(Komponenter!F7:F31,"OK")+COUNTIF(Komponenter!F7:F31,"Ikke med")&lt;&gt;25,"FEIL: kontroller aktive rader i Komponenter.",IF(AND(B7=0,SUM(Ventiler!D7:D31,Komponenter!D7:D31)&gt;0),"FEIL: ved null volumstrøm må komponenttrykkfall være 0.","OK")))))),"FEIL: kontroller beregningsformler.")),IF(AND(Trykkberegning!E34&lt;&gt;"Hoveddimensjon",Trykkberegning!E34&lt;&gt;"Rørstrekk-tabell"),"FEIL: velg beregningsmetode for rette rør.",IF(COUNTIF(Reduksjoner!K7:K31,"OK")+COUNTIF(Reduksjoner!K7:K31,"Ikke med")&lt;&gt;25,"FEIL: kontroller Reduksjoner.",IF(AND(Trykkberegning!E34="Rørstrekk-tabell",COUNTIF(Rørstrekk!I7:I31,"OK")+COUNTIF(Rørstrekk!I7:I31,"Ikke med")&lt;&gt;25),"FEIL: kontroller Rørstrekk.","OK")))),"FEIL: kontroller nye inndata.")</f>
@@ -5606,13 +6697,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>365</v>
+        <v>436</v>
       </c>
       <c r="B6" s="35" t="n">
         <v>9.80665</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>366</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5624,12 +6715,12 @@
         <v>0.01</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>367</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>368</v>
+        <v>439</v>
       </c>
       <c r="B8" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",Trykkberegning!E12/1000,""),"")</f>
@@ -5641,19 +6732,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>369</v>
+        <v>440</v>
       </c>
       <c r="B9" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",Trykkberegning!E22/1000,""),"")</f>
         <v>0.001002</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>370</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>371</v>
+        <v>442</v>
       </c>
       <c r="B10" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",Trykkberegning!E21,""),"")</f>
@@ -5665,7 +6756,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>372</v>
+        <v>443</v>
       </c>
       <c r="B11" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",Trykkberegning!E15/1000,""),"")</f>
@@ -5677,31 +6768,31 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
       <c r="B12" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",PI()*B8^2/4,""),"")</f>
         <v>0.00534561624962388</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>374</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>375</v>
+        <v>446</v>
       </c>
       <c r="B13" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",B7/B12,""),"")</f>
         <v>1.87069170943642</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>376</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>377</v>
+        <v>448</v>
       </c>
       <c r="B14" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",B10*B13*B8/B9,""),"")</f>
@@ -5713,7 +6804,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>378</v>
+        <v>449</v>
       </c>
       <c r="B15" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",B11/B8,""),"")</f>
@@ -5725,7 +6816,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
-        <v>379</v>
+        <v>450</v>
       </c>
       <c r="B16" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",IF(B14=0,0,IF(B14&lt;2300,64/B14,(-1.8*LOG10((B15/3.7)^1.11+6.9/B14))^(-2))),""),"")</f>
@@ -5737,7 +6828,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>380</v>
+        <v>451</v>
       </c>
       <c r="B17" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",IF(B14=0,0,IF(B14&lt;2300,B16,(-2*LOG10(B15/3.7+2.51/(B14*SQRT(B16))))^(-2))),""),"")</f>
@@ -5749,7 +6840,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>381</v>
+        <v>452</v>
       </c>
       <c r="B18" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",IF(B14=0,0,IF(B14&lt;2300,B16,(-2*LOG10(B15/3.7+2.51/(B14*SQRT(B17))))^(-2))),""),"")</f>
@@ -5761,7 +6852,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>382</v>
+        <v>453</v>
       </c>
       <c r="B19" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",IF(B14=0,0,IF(B14&lt;2300,B16,(-2*LOG10(B15/3.7+2.51/(B14*SQRT(B18))))^(-2))),""),"")</f>
@@ -5773,7 +6864,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
-        <v>383</v>
+        <v>454</v>
       </c>
       <c r="B20" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",IF(B14=0,0,IF(B14&lt;2300,B16,(-2*LOG10(B15/3.7+2.51/(B14*SQRT(B19))))^(-2))),""),"")</f>
@@ -5785,7 +6876,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>384</v>
+        <v>455</v>
       </c>
       <c r="B21" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",IF(B14=0,0,IF(B14&lt;2300,B16,(-2*LOG10(B15/3.7+2.51/(B14*SQRT(B20))))^(-2))),""),"")</f>
@@ -5797,7 +6888,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>385</v>
+        <v>456</v>
       </c>
       <c r="B22" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",IF(B14=0,0,IF(B14&lt;2300,B16,(-2*LOG10(B15/3.7+2.51/(B14*SQRT(B21))))^(-2))),""),"")</f>
@@ -5809,7 +6900,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>386</v>
+        <v>457</v>
       </c>
       <c r="B23" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",B22,""),"")</f>
@@ -5821,7 +6912,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>387</v>
+        <v>458</v>
       </c>
       <c r="B24" s="27" t="str">
         <f aca="false">IFERROR(IF(B3="OK",IF(B14=0,"Ingen strømning",IF(B14&lt;2300,"Laminært",IF(B14&lt;4000,"Overgang","Turbulent"))),""),"")</f>
@@ -5831,14 +6922,14 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
-        <v>388</v>
+        <v>459</v>
       </c>
       <c r="B25" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",B10*B13^2/2,""),"")</f>
         <v>1746.5941971525</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5855,17 +6946,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>390</v>
+        <v>461</v>
       </c>
       <c r="B29" s="35" t="n">
         <f aca="false">IFERROR(IF(B4="OK",IF(Trykkberegning!E34="Rørstrekk-tabell",SUM(Rørstrekk!H7:H31)*1000,B23*Trykkberegning!E29/B8*B25),""),"")</f>
         <v>41342.7391377765</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="E29" s="27" t="s">
         <v>72</v>
@@ -5873,100 +6964,100 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="27" t="s">
-        <v>392</v>
+        <v>463</v>
       </c>
       <c r="B30" s="35" t="n">
         <f aca="false">IFERROR(IF(B4="OK",SUM(Bend!I7:I31)*1000,""),"")</f>
         <v>2243.74066707195</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="D30" s="27" t="str">
         <f aca="false">IF(AND(B4="OK",E30&lt;&gt;0),"Rørfriksjon","")</f>
         <v>Rørfriksjon</v>
       </c>
-      <c r="E30" s="46" t="n">
+      <c r="E30" s="47" t="n">
         <f aca="false">IF(B4="OK",B29/100000,0)</f>
         <v>0.413427391377765</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
       <c r="B31" s="35" t="n">
         <f aca="false">IFERROR(IF(B4="OK",SUM(Ventiler!D7:D31)*1000,""),"")</f>
         <v>0</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="D31" s="27" t="str">
         <f aca="false">IF(AND(B4="OK",E31&lt;&gt;0),"Bend / K","")</f>
         <v>Bend / K</v>
       </c>
-      <c r="E31" s="46" t="n">
+      <c r="E31" s="47" t="n">
         <f aca="false">IF(B4="OK",B30/100000,0)</f>
         <v>0.0224374066707195</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="27" t="s">
-        <v>394</v>
+        <v>465</v>
       </c>
       <c r="B32" s="35" t="n">
         <f aca="false">IFERROR(IF(B4="OK",SUM(Komponenter!D7:D31)*1000,""),"")</f>
         <v>0</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="D32" s="27" t="str">
         <f aca="false">IF(AND(B4="OK",E32&lt;&gt;0),"Ventiler","")</f>
         <v/>
       </c>
-      <c r="E32" s="46" t="n">
+      <c r="E32" s="47" t="n">
         <f aca="false">IF(B4="OK",B31/100000,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>395</v>
+        <v>466</v>
       </c>
       <c r="B33" s="35" t="n">
         <f aca="false">IFERROR(IF(B4="OK",IF(Trykkberegning!E17=0,0,Trykkberegning!E17*Trykkberegning!E18*B25),""),"")</f>
         <v>0</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="D33" s="27" t="str">
         <f aca="false">IF(AND(B4="OK",E33&lt;&gt;0),"Flenskoblinger","")</f>
         <v/>
       </c>
-      <c r="E33" s="46" t="n">
+      <c r="E33" s="47" t="n">
         <f aca="false">IF(B4="OK",B33/100000,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="27" t="s">
-        <v>396</v>
+        <v>467</v>
       </c>
       <c r="B34" s="0" t="n">
         <f aca="false">IFERROR(IF(B4="OK",SUM(Reduksjoner!J7:J31)*1000,""),"")</f>
         <v>0</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="D34" s="27" t="str">
         <f aca="false">IF(AND(B4="OK",E34&lt;&gt;0),"Andre komponenter","")</f>
         <v/>
       </c>
-      <c r="E34" s="46" t="n">
+      <c r="E34" s="47" t="n">
         <f aca="false">IF(B4="OK",B32/100000,0)</f>
         <v>0</v>
       </c>
@@ -5980,60 +7071,60 @@
         <v>43586.4798048485</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="D35" s="27" t="str">
         <f aca="false">IF(AND(B4="OK",E35&lt;&gt;0),"Høydebidrag","")</f>
         <v>Høydebidrag</v>
       </c>
-      <c r="E35" s="46" t="n">
+      <c r="E35" s="47" t="n">
         <f aca="false">IF(B4="OK",B36/100000,0)</f>
         <v>0.7831198424</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="27" t="s">
-        <v>397</v>
+        <v>468</v>
       </c>
       <c r="B36" s="35" t="n">
         <f aca="false">IFERROR(IF(B4="OK",B10*B6*B26,""),"")</f>
         <v>78311.98424</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="D36" s="27" t="str">
         <f aca="false">IF(AND(B4="OK",E36&lt;&gt;0),"Reduksjoner","")</f>
         <v/>
       </c>
-      <c r="E36" s="46" t="n">
+      <c r="E36" s="47" t="n">
         <f aca="false">IF(B4="OK",B34/100000,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="27" t="s">
-        <v>398</v>
+        <v>469</v>
       </c>
       <c r="B37" s="35" t="n">
         <f aca="false">IFERROR(IF(B4="OK",B35+B36+B40,""),"")</f>
         <v>121898.464044849</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="D37" s="27" t="str">
         <f aca="false">IF(AND(B4="OK",E37&lt;&gt;0),"Hastighetsbidrag","")</f>
         <v/>
       </c>
-      <c r="E37" s="46" t="n">
+      <c r="E37" s="47" t="n">
         <f aca="false">IF(B4="OK",B40/100000,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="27" t="s">
-        <v>399</v>
+        <v>470</v>
       </c>
       <c r="B38" s="35" t="n">
         <f aca="false">IFERROR(IF(B3="OK",IF(B14&lt;2300,0,1/SQRT(B23)+2*LOG10(B15/3.7+2.51/(B14*SQRT(B23)))),""),"")</f>
@@ -6045,14 +7136,14 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
-        <v>400</v>
+        <v>471</v>
       </c>
       <c r="B40" s="35" t="n">
         <f aca="false">IFERROR(IF(B4="OK",B10/2*((B7/(PI()*(Reduksjoner!F4/1000)^2/4))^2-B13^2),""),"")</f>
         <v>0</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -6069,7 +7160,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -6079,25 +7170,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>401</v>
+        <v>472</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>403</v>
+        <v>474</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>322</v>
+        <v>393</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>404</v>
+        <v>475</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>405</v>
+        <v>476</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>406</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6105,19 +7196,19 @@
         <v>5</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>284</v>
+        <v>355</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>407</v>
+        <v>478</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>352</v>
+        <v>423</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>155</v>
@@ -6129,24 +7220,24 @@
         <v>1.5</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>408</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>243</v>
+        <v>201</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>287</v>
+        <v>358</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>329</v>
+        <v>400</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>409</v>
+        <v>480</v>
       </c>
       <c r="F3" s="0" t="s">
         <v>36</v>
@@ -6161,56 +7252,56 @@
         <v>1</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>410</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>283</v>
+        <v>354</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>289</v>
+        <v>360</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>331</v>
+        <v>402</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>354</v>
+        <v>425</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
       <c r="J4" s="0" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>412</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>291</v>
+        <v>362</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>335</v>
+        <v>406</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>413</v>
+        <v>484</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>355</v>
+        <v>426</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>157</v>
@@ -6222,24 +7313,24 @@
         <v>0</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>412</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>293</v>
+        <v>364</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>339</v>
+        <v>410</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>356</v>
+        <v>427</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>156</v>
@@ -6251,62 +7342,62 @@
         <v>0</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>412</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>295</v>
+        <v>366</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>341</v>
+        <v>412</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>415</v>
+        <v>486</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>357</v>
+        <v>428</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>416</v>
+        <v>487</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>416</v>
+        <v>487</v>
       </c>
       <c r="J7" s="0" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>412</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>297</v>
+        <v>368</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>417</v>
+        <v>488</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>359</v>
+        <v>430</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>418</v>
+        <v>489</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>418</v>
+        <v>489</v>
       </c>
       <c r="J8" s="0" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>419</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6314,86 +7405,86 @@
         <v>8</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>299</v>
+        <v>370</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>420</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>301</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>258</v>
+        <v>216</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>303</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>305</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>262</v>
+        <v>220</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>307</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>309</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>311</v>
+        <v>382</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>421</v>
+        <v>492</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>313</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="0" t="s">
-        <v>315</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="0" t="s">
-        <v>317</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="0" t="s">
-        <v>319</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="0" t="s">
-        <v>421</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -11725,20 +12816,25 @@
     <tabColor rgb="FF087F8C"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:AB54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="28" min="19" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11799,6 +12895,11 @@
       <c r="K4" s="36"/>
       <c r="L4" s="36"/>
       <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="s">
@@ -11816,8 +12917,13 @@
       <c r="K5" s="37"/>
       <c r="L5" s="37"/>
       <c r="M5" s="37"/>
-    </row>
-    <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+    </row>
+    <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
         <v>165</v>
       </c>
@@ -11857,10 +12963,25 @@
       <c r="M6" s="27" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N6" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="O6" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="P6" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q6" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="R6" s="27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B7" s="18" t="n">
         <v>0</v>
@@ -11872,33 +12993,90 @@
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B7="",B7=0),"Ikke med",IF(OR(NOT(ISNUMBER(B7)),B7&lt;0,B7&lt;&gt;INT(B7)),"FEIL: antall",IF(A7="","FEIL: angi ventil",IF(AND(C7&lt;&gt;"",OR(NOT(ISNUMBER(C7)),C7&lt;0)),"FEIL: trykkfall",IF(AND(C7="",OR(NOT(ISNUMBER(H7)),H7&lt;=0,G7="",NOT(ISNUMBER(I7)),I7&lt;=0,I7&gt;100,E7="",M7&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B7="",B7=0),"Ikke med",IF(OR(NOT(ISNUMBER(B7)),B7&lt;0,B7&lt;&gt;INT(B7)),"FEIL: antall",IF(A7="","FEIL: angi ventil",IF(AND(C7&lt;&gt;"",OR(NOT(ISNUMBER(C7)),C7&lt;0)),"FEIL: trykkfall",IF(AND(C7="",H7&lt;&gt;"",OR(NOT(ISNUMBER(H7)),H7&lt;=0,G7="",NOT(ISNUMBER(I7)),I7&lt;=0,I7&gt;100,E7="",M7&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C7="",H7="",OR(NOT(ISNUMBER(Q7)),Q7&lt;=0)),"FEIL: lokal ID",IF(AND(C7="",H7="",ABS(Q7-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q7)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C7="",H7="",N7&lt;&gt;"",OR(NOT(ISNUMBER(N7)),N7&lt;0,E7="",NOT(ISNUMBER(I7)),I7&lt;=0,I7&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C7="",H7="",N7="",OR(Z7&lt;=0,AND(AB7&lt;&gt;"",G7&lt;&gt;AB7))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C7="",H7="",N7="",I7&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C7="",H7="",N7="",AA7&gt;0,AA7&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G7" s="16"/>
+      <c r="G7" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H7" s="16"/>
       <c r="I7" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="J7" s="14" t="str">
-        <f aca="false">IFERROR(IF(C7&lt;&gt;"",C7,IF(AND(H7&gt;0,ISNUMBER(H7)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H7)^2,"")),"")</f>
-        <v/>
-      </c>
-      <c r="K7" s="27" t="n">
+      <c r="J7" s="14" t="n">
+        <f aca="false">IFERROR(IF(C7&lt;&gt;"",C7,IF(H7&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H7)^2,IF(ISNUMBER(O7),O7*Beregning!$B$25*(Trykkberegning!$E$12/Q7)^4/1000,""))),"")</f>
+        <v>0.0890498267876532</v>
+      </c>
+      <c r="K7" s="27" t="str">
         <f aca="false">IFERROR(VLOOKUP(A7,Ventiloppslag,4,FALSE()),"")</f>
-        <v>0</v>
+        <v>https://raw.githubusercontent.com/CalebBell/fluids/master/fluids/fittings.py</v>
       </c>
       <c r="L7" s="27" t="str">
-        <f aca="false">IF(C7&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C7&lt;&gt;"","Eget trykkfall",IF(H7&lt;&gt;"","Dokumentert Kv",IF(N7&lt;&gt;"","Eget K",IF(Z7&lt;=0,"Ingen generell modell",IF(A7="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Modellestimat: Crane, full åpning</v>
       </c>
       <c r="M7" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N7" s="42"/>
+      <c r="O7" s="35" t="n">
+        <f aca="false">IFERROR(IF(C7&lt;&gt;"","",IF(H7&lt;&gt;"",200*(3600*PI()*(Q7/1000)^2/4/H7)^2,IF(N7&lt;&gt;"",N7,IF(Z7&gt;0,Z7*Y7,"")))),"")</f>
+        <v>0.0509848406303151</v>
+      </c>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="14" t="n">
+        <f aca="false">IF(P7="",Trykkberegning!$E$12,P7)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R7" s="14" t="n">
+        <f aca="false">IFERROR(IF(O7&gt;0,3600*PI()*(Q7/1000)^2/4*SQRT(200/O7),""),"")</f>
+        <v>1205.29885504198</v>
+      </c>
+      <c r="S7" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q7/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q7/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T7" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q7/1000)^(-1.0112))/3.7+2.51/((7500000*(Q7/1000))*SQRT(S7))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U7" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q7/1000)^(-1.0112))/3.7+2.51/((7500000*(Q7/1000))*SQRT(T7))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V7" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q7/1000)^(-1.0112))/3.7+2.51/((7500000*(Q7/1000))*SQRT(U7))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W7" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q7/1000)^(-1.0112))/3.7+2.51/((7500000*(Q7/1000))*SQRT(V7))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X7" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q7/1000)^(-1.0112))/3.7+2.51/((7500000*(Q7/1000))*SQRT(W7))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y7" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q7/1000)^(-1.0112))/3.7+2.51/((7500000*(Q7/1000))*SQRT(X7))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z7" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A7&amp;"|"&amp;G7,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AA7" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q7,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB7" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q7-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B8" s="18" t="n">
         <v>0</v>
@@ -11910,33 +13088,90 @@
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B8="",B8=0),"Ikke med",IF(OR(NOT(ISNUMBER(B8)),B8&lt;0,B8&lt;&gt;INT(B8)),"FEIL: antall",IF(A8="","FEIL: angi ventil",IF(AND(C8&lt;&gt;"",OR(NOT(ISNUMBER(C8)),C8&lt;0)),"FEIL: trykkfall",IF(AND(C8="",OR(NOT(ISNUMBER(H8)),H8&lt;=0,G8="",NOT(ISNUMBER(I8)),I8&lt;=0,I8&gt;100,E8="",M8&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B8="",B8=0),"Ikke med",IF(OR(NOT(ISNUMBER(B8)),B8&lt;0,B8&lt;&gt;INT(B8)),"FEIL: antall",IF(A8="","FEIL: angi ventil",IF(AND(C8&lt;&gt;"",OR(NOT(ISNUMBER(C8)),C8&lt;0)),"FEIL: trykkfall",IF(AND(C8="",H8&lt;&gt;"",OR(NOT(ISNUMBER(H8)),H8&lt;=0,G8="",NOT(ISNUMBER(I8)),I8&lt;=0,I8&gt;100,E8="",M8&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C8="",H8="",OR(NOT(ISNUMBER(Q8)),Q8&lt;=0)),"FEIL: lokal ID",IF(AND(C8="",H8="",ABS(Q8-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q8)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C8="",H8="",N8&lt;&gt;"",OR(NOT(ISNUMBER(N8)),N8&lt;0,E8="",NOT(ISNUMBER(I8)),I8&lt;=0,I8&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C8="",H8="",N8="",OR(Z8&lt;=0,AND(AB8&lt;&gt;"",G8&lt;&gt;AB8))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C8="",H8="",N8="",I8&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C8="",H8="",N8="",AA8&gt;0,AA8&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G8" s="16"/>
+      <c r="G8" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H8" s="16"/>
       <c r="I8" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="J8" s="14" t="str">
-        <f aca="false">IFERROR(IF(C8&lt;&gt;"",C8,IF(AND(H8&gt;0,ISNUMBER(H8)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H8)^2,"")),"")</f>
-        <v/>
-      </c>
-      <c r="K8" s="27" t="n">
+      <c r="J8" s="14" t="n">
+        <f aca="false">IFERROR(IF(C8&lt;&gt;"",C8,IF(H8&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H8)^2,IF(ISNUMBER(O8),O8*Beregning!$B$25*(Trykkberegning!$E$12/Q8)^4/1000,""))),"")</f>
+        <v>0.237466204767075</v>
+      </c>
+      <c r="K8" s="27" t="str">
         <f aca="false">IFERROR(VLOOKUP(A8,Ventiloppslag,4,FALSE()),"")</f>
-        <v>0</v>
+        <v>https://raw.githubusercontent.com/CalebBell/fluids/master/fluids/fittings.py</v>
       </c>
       <c r="L8" s="27" t="str">
-        <f aca="false">IF(C8&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C8&lt;&gt;"","Eget trykkfall",IF(H8&lt;&gt;"","Dokumentert Kv",IF(N8&lt;&gt;"","Eget K",IF(Z8&lt;=0,"Ingen generell modell",IF(A8="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>ANSLAG: skyvespjeld fra sluse</v>
       </c>
       <c r="M8" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N8" s="42"/>
+      <c r="O8" s="35" t="n">
+        <f aca="false">IFERROR(IF(C8&lt;&gt;"","",IF(H8&lt;&gt;"",200*(3600*PI()*(Q8/1000)^2/4/H8)^2,IF(N8&lt;&gt;"",N8,IF(Z8&gt;0,Z8*Y8,"")))),"")</f>
+        <v>0.135959575014174</v>
+      </c>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="14" t="n">
+        <f aca="false">IF(P8="",Trykkberegning!$E$12,P8)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R8" s="14" t="n">
+        <f aca="false">IFERROR(IF(O8&gt;0,3600*PI()*(Q8/1000)^2/4*SQRT(200/O8),""),"")</f>
+        <v>738.091795603408</v>
+      </c>
+      <c r="S8" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q8/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q8/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T8" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q8/1000)^(-1.0112))/3.7+2.51/((7500000*(Q8/1000))*SQRT(S8))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U8" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q8/1000)^(-1.0112))/3.7+2.51/((7500000*(Q8/1000))*SQRT(T8))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V8" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q8/1000)^(-1.0112))/3.7+2.51/((7500000*(Q8/1000))*SQRT(U8))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W8" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q8/1000)^(-1.0112))/3.7+2.51/((7500000*(Q8/1000))*SQRT(V8))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X8" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q8/1000)^(-1.0112))/3.7+2.51/((7500000*(Q8/1000))*SQRT(W8))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y8" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q8/1000)^(-1.0112))/3.7+2.51/((7500000*(Q8/1000))*SQRT(X8))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z8" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A8&amp;"|"&amp;G8,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>8</v>
+      </c>
+      <c r="AA8" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q8,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB8" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q8-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>0</v>
@@ -11948,33 +13183,90 @@
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B9="",B9=0),"Ikke med",IF(OR(NOT(ISNUMBER(B9)),B9&lt;0,B9&lt;&gt;INT(B9)),"FEIL: antall",IF(A9="","FEIL: angi ventil",IF(AND(C9&lt;&gt;"",OR(NOT(ISNUMBER(C9)),C9&lt;0)),"FEIL: trykkfall",IF(AND(C9="",OR(NOT(ISNUMBER(H9)),H9&lt;=0,G9="",NOT(ISNUMBER(I9)),I9&lt;=0,I9&gt;100,E9="",M9&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B9="",B9=0),"Ikke med",IF(OR(NOT(ISNUMBER(B9)),B9&lt;0,B9&lt;&gt;INT(B9)),"FEIL: antall",IF(A9="","FEIL: angi ventil",IF(AND(C9&lt;&gt;"",OR(NOT(ISNUMBER(C9)),C9&lt;0)),"FEIL: trykkfall",IF(AND(C9="",H9&lt;&gt;"",OR(NOT(ISNUMBER(H9)),H9&lt;=0,G9="",NOT(ISNUMBER(I9)),I9&lt;=0,I9&gt;100,E9="",M9&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C9="",H9="",OR(NOT(ISNUMBER(Q9)),Q9&lt;=0)),"FEIL: lokal ID",IF(AND(C9="",H9="",ABS(Q9-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q9)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C9="",H9="",N9&lt;&gt;"",OR(NOT(ISNUMBER(N9)),N9&lt;0,E9="",NOT(ISNUMBER(I9)),I9&lt;=0,I9&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C9="",H9="",N9="",OR(Z9&lt;=0,AND(AB9&lt;&gt;"",G9&lt;&gt;AB9))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C9="",H9="",N9="",I9&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C9="",H9="",N9="",AA9&gt;0,AA9&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G9" s="16"/>
+      <c r="G9" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H9" s="16"/>
       <c r="I9" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="J9" s="14" t="str">
-        <f aca="false">IFERROR(IF(C9&lt;&gt;"",C9,IF(AND(H9&gt;0,ISNUMBER(H9)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H9)^2,"")),"")</f>
-        <v/>
-      </c>
-      <c r="K9" s="27" t="n">
+      <c r="J9" s="14" t="n">
+        <f aca="false">IFERROR(IF(C9&lt;&gt;"",C9,IF(H9&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H9)^2,IF(ISNUMBER(O9),O9*Beregning!$B$25*(Trykkberegning!$E$12/Q9)^4/1000,""))),"")</f>
+        <v>1.3357474018148</v>
+      </c>
+      <c r="K9" s="27" t="str">
         <f aca="false">IFERROR(VLOOKUP(A9,Ventiloppslag,4,FALSE()),"")</f>
-        <v>0</v>
+        <v>https://raw.githubusercontent.com/CalebBell/fluids/master/fluids/fittings.py</v>
       </c>
       <c r="L9" s="27" t="str">
-        <f aca="false">IF(C9&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C9&lt;&gt;"","Eget trykkfall",IF(H9&lt;&gt;"","Dokumentert Kv",IF(N9&lt;&gt;"","Eget K",IF(Z9&lt;=0,"Ingen generell modell",IF(A9="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Modellestimat: Crane, full åpning</v>
       </c>
       <c r="M9" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N9" s="42"/>
+      <c r="O9" s="35" t="n">
+        <f aca="false">IFERROR(IF(C9&lt;&gt;"","",IF(H9&lt;&gt;"",200*(3600*PI()*(Q9/1000)^2/4/H9)^2,IF(N9&lt;&gt;"",N9,IF(Z9&gt;0,Z9*Y9,"")))),"")</f>
+        <v>0.764772609454727</v>
+      </c>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="14" t="n">
+        <f aca="false">IF(P9="",Trykkberegning!$E$12,P9)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R9" s="14" t="n">
+        <f aca="false">IFERROR(IF(O9&gt;0,3600*PI()*(Q9/1000)^2/4*SQRT(200/O9),""),"")</f>
+        <v>311.206826185363</v>
+      </c>
+      <c r="S9" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q9/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q9/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T9" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q9/1000)^(-1.0112))/3.7+2.51/((7500000*(Q9/1000))*SQRT(S9))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U9" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q9/1000)^(-1.0112))/3.7+2.51/((7500000*(Q9/1000))*SQRT(T9))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V9" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q9/1000)^(-1.0112))/3.7+2.51/((7500000*(Q9/1000))*SQRT(U9))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W9" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q9/1000)^(-1.0112))/3.7+2.51/((7500000*(Q9/1000))*SQRT(V9))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X9" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q9/1000)^(-1.0112))/3.7+2.51/((7500000*(Q9/1000))*SQRT(W9))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y9" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q9/1000)^(-1.0112))/3.7+2.51/((7500000*(Q9/1000))*SQRT(X9))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z9" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A9&amp;"|"&amp;G9,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>45</v>
+      </c>
+      <c r="AA9" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q9,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB9" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q9-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>0</v>
@@ -11986,16 +13278,19 @@
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B10="",B10=0),"Ikke med",IF(OR(NOT(ISNUMBER(B10)),B10&lt;0,B10&lt;&gt;INT(B10)),"FEIL: antall",IF(A10="","FEIL: angi ventil",IF(AND(C10&lt;&gt;"",OR(NOT(ISNUMBER(C10)),C10&lt;0)),"FEIL: trykkfall",IF(AND(C10="",OR(NOT(ISNUMBER(H10)),H10&lt;=0,G10="",NOT(ISNUMBER(I10)),I10&lt;=0,I10&gt;100,E10="",M10&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B10="",B10=0),"Ikke med",IF(OR(NOT(ISNUMBER(B10)),B10&lt;0,B10&lt;&gt;INT(B10)),"FEIL: antall",IF(A10="","FEIL: angi ventil",IF(AND(C10&lt;&gt;"",OR(NOT(ISNUMBER(C10)),C10&lt;0)),"FEIL: trykkfall",IF(AND(C10="",H10&lt;&gt;"",OR(NOT(ISNUMBER(H10)),H10&lt;=0,G10="",NOT(ISNUMBER(I10)),I10&lt;=0,I10&gt;100,E10="",M10&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C10="",H10="",OR(NOT(ISNUMBER(Q10)),Q10&lt;=0)),"FEIL: lokal ID",IF(AND(C10="",H10="",ABS(Q10-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q10)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C10="",H10="",N10&lt;&gt;"",OR(NOT(ISNUMBER(N10)),N10&lt;0,E10="",NOT(ISNUMBER(I10)),I10&lt;=0,I10&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C10="",H10="",N10="",OR(Z10&lt;=0,AND(AB10&lt;&gt;"",G10&lt;&gt;AB10))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C10="",H10="",N10="",I10&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C10="",H10="",N10="",AA10&gt;0,AA10&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G10" s="16"/>
+      <c r="G10" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H10" s="16"/>
       <c r="I10" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J10" s="14" t="str">
-        <f aca="false">IFERROR(IF(C10&lt;&gt;"",C10,IF(AND(H10&gt;0,ISNUMBER(H10)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H10)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C10&lt;&gt;"",C10,IF(H10&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H10)^2,IF(ISNUMBER(O10),O10*Beregning!$B$25*(Trykkberegning!$E$12/Q10)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K10" s="27" t="n">
@@ -12003,16 +13298,70 @@
         <v>0</v>
       </c>
       <c r="L10" s="27" t="str">
-        <f aca="false">IF(C10&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C10&lt;&gt;"","Eget trykkfall",IF(H10&lt;&gt;"","Dokumentert Kv",IF(N10&lt;&gt;"","Eget K",IF(Z10&lt;=0,"Ingen generell modell",IF(A10="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N10" s="42"/>
+      <c r="O10" s="35" t="str">
+        <f aca="false">IFERROR(IF(C10&lt;&gt;"","",IF(H10&lt;&gt;"",200*(3600*PI()*(Q10/1000)^2/4/H10)^2,IF(N10&lt;&gt;"",N10,IF(Z10&gt;0,Z10*Y10,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="14" t="n">
+        <f aca="false">IF(P10="",Trykkberegning!$E$12,P10)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R10" s="14" t="str">
+        <f aca="false">IFERROR(IF(O10&gt;0,3600*PI()*(Q10/1000)^2/4*SQRT(200/O10),""),"")</f>
+        <v/>
+      </c>
+      <c r="S10" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q10/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q10/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T10" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q10/1000)^(-1.0112))/3.7+2.51/((7500000*(Q10/1000))*SQRT(S10))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U10" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q10/1000)^(-1.0112))/3.7+2.51/((7500000*(Q10/1000))*SQRT(T10))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V10" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q10/1000)^(-1.0112))/3.7+2.51/((7500000*(Q10/1000))*SQRT(U10))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W10" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q10/1000)^(-1.0112))/3.7+2.51/((7500000*(Q10/1000))*SQRT(V10))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X10" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q10/1000)^(-1.0112))/3.7+2.51/((7500000*(Q10/1000))*SQRT(W10))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y10" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q10/1000)^(-1.0112))/3.7+2.51/((7500000*(Q10/1000))*SQRT(X10))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z10" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A10&amp;"|"&amp;G10,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q10,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB10" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q10-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B11" s="18" t="n">
         <v>0</v>
@@ -12024,16 +13373,19 @@
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B11="",B11=0),"Ikke med",IF(OR(NOT(ISNUMBER(B11)),B11&lt;0,B11&lt;&gt;INT(B11)),"FEIL: antall",IF(A11="","FEIL: angi ventil",IF(AND(C11&lt;&gt;"",OR(NOT(ISNUMBER(C11)),C11&lt;0)),"FEIL: trykkfall",IF(AND(C11="",OR(NOT(ISNUMBER(H11)),H11&lt;=0,G11="",NOT(ISNUMBER(I11)),I11&lt;=0,I11&gt;100,E11="",M11&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B11="",B11=0),"Ikke med",IF(OR(NOT(ISNUMBER(B11)),B11&lt;0,B11&lt;&gt;INT(B11)),"FEIL: antall",IF(A11="","FEIL: angi ventil",IF(AND(C11&lt;&gt;"",OR(NOT(ISNUMBER(C11)),C11&lt;0)),"FEIL: trykkfall",IF(AND(C11="",H11&lt;&gt;"",OR(NOT(ISNUMBER(H11)),H11&lt;=0,G11="",NOT(ISNUMBER(I11)),I11&lt;=0,I11&gt;100,E11="",M11&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C11="",H11="",OR(NOT(ISNUMBER(Q11)),Q11&lt;=0)),"FEIL: lokal ID",IF(AND(C11="",H11="",ABS(Q11-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q11)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C11="",H11="",N11&lt;&gt;"",OR(NOT(ISNUMBER(N11)),N11&lt;0,E11="",NOT(ISNUMBER(I11)),I11&lt;=0,I11&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C11="",H11="",N11="",OR(Z11&lt;=0,AND(AB11&lt;&gt;"",G11&lt;&gt;AB11))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C11="",H11="",N11="",I11&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C11="",H11="",N11="",AA11&gt;0,AA11&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G11" s="16"/>
+      <c r="G11" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H11" s="16"/>
       <c r="I11" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J11" s="14" t="str">
-        <f aca="false">IFERROR(IF(C11&lt;&gt;"",C11,IF(AND(H11&gt;0,ISNUMBER(H11)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H11)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C11&lt;&gt;"",C11,IF(H11&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H11)^2,IF(ISNUMBER(O11),O11*Beregning!$B$25*(Trykkberegning!$E$12/Q11)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K11" s="27" t="n">
@@ -12041,14 +13393,68 @@
         <v>0</v>
       </c>
       <c r="L11" s="27" t="str">
-        <f aca="false">IF(C11&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C11&lt;&gt;"","Eget trykkfall",IF(H11&lt;&gt;"","Dokumentert Kv",IF(N11&lt;&gt;"","Eget K",IF(Z11&lt;=0,"Ingen generell modell",IF(A11="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M11" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N11" s="42"/>
+      <c r="O11" s="35" t="str">
+        <f aca="false">IFERROR(IF(C11&lt;&gt;"","",IF(H11&lt;&gt;"",200*(3600*PI()*(Q11/1000)^2/4/H11)^2,IF(N11&lt;&gt;"",N11,IF(Z11&gt;0,Z11*Y11,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="14" t="n">
+        <f aca="false">IF(P11="",Trykkberegning!$E$12,P11)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R11" s="14" t="str">
+        <f aca="false">IFERROR(IF(O11&gt;0,3600*PI()*(Q11/1000)^2/4*SQRT(200/O11),""),"")</f>
+        <v/>
+      </c>
+      <c r="S11" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q11/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q11/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T11" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q11/1000)^(-1.0112))/3.7+2.51/((7500000*(Q11/1000))*SQRT(S11))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U11" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q11/1000)^(-1.0112))/3.7+2.51/((7500000*(Q11/1000))*SQRT(T11))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V11" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q11/1000)^(-1.0112))/3.7+2.51/((7500000*(Q11/1000))*SQRT(U11))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W11" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q11/1000)^(-1.0112))/3.7+2.51/((7500000*(Q11/1000))*SQRT(V11))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X11" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q11/1000)^(-1.0112))/3.7+2.51/((7500000*(Q11/1000))*SQRT(W11))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y11" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q11/1000)^(-1.0112))/3.7+2.51/((7500000*(Q11/1000))*SQRT(X11))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z11" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A11&amp;"|"&amp;G11,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA11" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q11,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB11" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q11-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6"/>
       <c r="B12" s="18" t="n">
         <v>0</v>
@@ -12060,16 +13466,19 @@
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B12="",B12=0),"Ikke med",IF(OR(NOT(ISNUMBER(B12)),B12&lt;0,B12&lt;&gt;INT(B12)),"FEIL: antall",IF(A12="","FEIL: angi ventil",IF(AND(C12&lt;&gt;"",OR(NOT(ISNUMBER(C12)),C12&lt;0)),"FEIL: trykkfall",IF(AND(C12="",OR(NOT(ISNUMBER(H12)),H12&lt;=0,G12="",NOT(ISNUMBER(I12)),I12&lt;=0,I12&gt;100,E12="",M12&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B12="",B12=0),"Ikke med",IF(OR(NOT(ISNUMBER(B12)),B12&lt;0,B12&lt;&gt;INT(B12)),"FEIL: antall",IF(A12="","FEIL: angi ventil",IF(AND(C12&lt;&gt;"",OR(NOT(ISNUMBER(C12)),C12&lt;0)),"FEIL: trykkfall",IF(AND(C12="",H12&lt;&gt;"",OR(NOT(ISNUMBER(H12)),H12&lt;=0,G12="",NOT(ISNUMBER(I12)),I12&lt;=0,I12&gt;100,E12="",M12&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C12="",H12="",OR(NOT(ISNUMBER(Q12)),Q12&lt;=0)),"FEIL: lokal ID",IF(AND(C12="",H12="",ABS(Q12-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q12)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C12="",H12="",N12&lt;&gt;"",OR(NOT(ISNUMBER(N12)),N12&lt;0,E12="",NOT(ISNUMBER(I12)),I12&lt;=0,I12&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C12="",H12="",N12="",OR(Z12&lt;=0,AND(AB12&lt;&gt;"",G12&lt;&gt;AB12))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C12="",H12="",N12="",I12&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C12="",H12="",N12="",AA12&gt;0,AA12&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G12" s="16"/>
+      <c r="G12" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H12" s="16"/>
       <c r="I12" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J12" s="14" t="str">
-        <f aca="false">IFERROR(IF(C12&lt;&gt;"",C12,IF(AND(H12&gt;0,ISNUMBER(H12)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H12)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C12&lt;&gt;"",C12,IF(H12&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H12)^2,IF(ISNUMBER(O12),O12*Beregning!$B$25*(Trykkberegning!$E$12/Q12)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K12" s="27" t="str">
@@ -12077,14 +13486,68 @@
         <v/>
       </c>
       <c r="L12" s="27" t="str">
-        <f aca="false">IF(C12&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C12&lt;&gt;"","Eget trykkfall",IF(H12&lt;&gt;"","Dokumentert Kv",IF(N12&lt;&gt;"","Eget K",IF(Z12&lt;=0,"Ingen generell modell",IF(A12="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N12" s="42"/>
+      <c r="O12" s="35" t="str">
+        <f aca="false">IFERROR(IF(C12&lt;&gt;"","",IF(H12&lt;&gt;"",200*(3600*PI()*(Q12/1000)^2/4/H12)^2,IF(N12&lt;&gt;"",N12,IF(Z12&gt;0,Z12*Y12,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="14" t="n">
+        <f aca="false">IF(P12="",Trykkberegning!$E$12,P12)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R12" s="14" t="str">
+        <f aca="false">IFERROR(IF(O12&gt;0,3600*PI()*(Q12/1000)^2/4*SQRT(200/O12),""),"")</f>
+        <v/>
+      </c>
+      <c r="S12" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q12/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q12/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T12" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q12/1000)^(-1.0112))/3.7+2.51/((7500000*(Q12/1000))*SQRT(S12))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U12" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q12/1000)^(-1.0112))/3.7+2.51/((7500000*(Q12/1000))*SQRT(T12))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V12" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q12/1000)^(-1.0112))/3.7+2.51/((7500000*(Q12/1000))*SQRT(U12))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W12" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q12/1000)^(-1.0112))/3.7+2.51/((7500000*(Q12/1000))*SQRT(V12))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X12" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q12/1000)^(-1.0112))/3.7+2.51/((7500000*(Q12/1000))*SQRT(W12))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y12" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q12/1000)^(-1.0112))/3.7+2.51/((7500000*(Q12/1000))*SQRT(X12))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z12" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A12&amp;"|"&amp;G12,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA12" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q12,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB12" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q12-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
       <c r="B13" s="18" t="n">
         <v>0</v>
@@ -12096,16 +13559,19 @@
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B13="",B13=0),"Ikke med",IF(OR(NOT(ISNUMBER(B13)),B13&lt;0,B13&lt;&gt;INT(B13)),"FEIL: antall",IF(A13="","FEIL: angi ventil",IF(AND(C13&lt;&gt;"",OR(NOT(ISNUMBER(C13)),C13&lt;0)),"FEIL: trykkfall",IF(AND(C13="",OR(NOT(ISNUMBER(H13)),H13&lt;=0,G13="",NOT(ISNUMBER(I13)),I13&lt;=0,I13&gt;100,E13="",M13&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B13="",B13=0),"Ikke med",IF(OR(NOT(ISNUMBER(B13)),B13&lt;0,B13&lt;&gt;INT(B13)),"FEIL: antall",IF(A13="","FEIL: angi ventil",IF(AND(C13&lt;&gt;"",OR(NOT(ISNUMBER(C13)),C13&lt;0)),"FEIL: trykkfall",IF(AND(C13="",H13&lt;&gt;"",OR(NOT(ISNUMBER(H13)),H13&lt;=0,G13="",NOT(ISNUMBER(I13)),I13&lt;=0,I13&gt;100,E13="",M13&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C13="",H13="",OR(NOT(ISNUMBER(Q13)),Q13&lt;=0)),"FEIL: lokal ID",IF(AND(C13="",H13="",ABS(Q13-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q13)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C13="",H13="",N13&lt;&gt;"",OR(NOT(ISNUMBER(N13)),N13&lt;0,E13="",NOT(ISNUMBER(I13)),I13&lt;=0,I13&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C13="",H13="",N13="",OR(Z13&lt;=0,AND(AB13&lt;&gt;"",G13&lt;&gt;AB13))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C13="",H13="",N13="",I13&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C13="",H13="",N13="",AA13&gt;0,AA13&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G13" s="16"/>
+      <c r="G13" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H13" s="16"/>
       <c r="I13" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J13" s="14" t="str">
-        <f aca="false">IFERROR(IF(C13&lt;&gt;"",C13,IF(AND(H13&gt;0,ISNUMBER(H13)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H13)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C13&lt;&gt;"",C13,IF(H13&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H13)^2,IF(ISNUMBER(O13),O13*Beregning!$B$25*(Trykkberegning!$E$12/Q13)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K13" s="27" t="str">
@@ -12113,14 +13579,68 @@
         <v/>
       </c>
       <c r="L13" s="27" t="str">
-        <f aca="false">IF(C13&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C13&lt;&gt;"","Eget trykkfall",IF(H13&lt;&gt;"","Dokumentert Kv",IF(N13&lt;&gt;"","Eget K",IF(Z13&lt;=0,"Ingen generell modell",IF(A13="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M13" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N13" s="42"/>
+      <c r="O13" s="35" t="str">
+        <f aca="false">IFERROR(IF(C13&lt;&gt;"","",IF(H13&lt;&gt;"",200*(3600*PI()*(Q13/1000)^2/4/H13)^2,IF(N13&lt;&gt;"",N13,IF(Z13&gt;0,Z13*Y13,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="14" t="n">
+        <f aca="false">IF(P13="",Trykkberegning!$E$12,P13)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R13" s="14" t="str">
+        <f aca="false">IFERROR(IF(O13&gt;0,3600*PI()*(Q13/1000)^2/4*SQRT(200/O13),""),"")</f>
+        <v/>
+      </c>
+      <c r="S13" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q13/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q13/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T13" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q13/1000)^(-1.0112))/3.7+2.51/((7500000*(Q13/1000))*SQRT(S13))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U13" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q13/1000)^(-1.0112))/3.7+2.51/((7500000*(Q13/1000))*SQRT(T13))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V13" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q13/1000)^(-1.0112))/3.7+2.51/((7500000*(Q13/1000))*SQRT(U13))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W13" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q13/1000)^(-1.0112))/3.7+2.51/((7500000*(Q13/1000))*SQRT(V13))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X13" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q13/1000)^(-1.0112))/3.7+2.51/((7500000*(Q13/1000))*SQRT(W13))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y13" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q13/1000)^(-1.0112))/3.7+2.51/((7500000*(Q13/1000))*SQRT(X13))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z13" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A13&amp;"|"&amp;G13,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA13" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q13,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB13" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q13-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6"/>
       <c r="B14" s="18" t="n">
         <v>0</v>
@@ -12132,16 +13652,19 @@
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B14="",B14=0),"Ikke med",IF(OR(NOT(ISNUMBER(B14)),B14&lt;0,B14&lt;&gt;INT(B14)),"FEIL: antall",IF(A14="","FEIL: angi ventil",IF(AND(C14&lt;&gt;"",OR(NOT(ISNUMBER(C14)),C14&lt;0)),"FEIL: trykkfall",IF(AND(C14="",OR(NOT(ISNUMBER(H14)),H14&lt;=0,G14="",NOT(ISNUMBER(I14)),I14&lt;=0,I14&gt;100,E14="",M14&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B14="",B14=0),"Ikke med",IF(OR(NOT(ISNUMBER(B14)),B14&lt;0,B14&lt;&gt;INT(B14)),"FEIL: antall",IF(A14="","FEIL: angi ventil",IF(AND(C14&lt;&gt;"",OR(NOT(ISNUMBER(C14)),C14&lt;0)),"FEIL: trykkfall",IF(AND(C14="",H14&lt;&gt;"",OR(NOT(ISNUMBER(H14)),H14&lt;=0,G14="",NOT(ISNUMBER(I14)),I14&lt;=0,I14&gt;100,E14="",M14&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C14="",H14="",OR(NOT(ISNUMBER(Q14)),Q14&lt;=0)),"FEIL: lokal ID",IF(AND(C14="",H14="",ABS(Q14-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q14)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C14="",H14="",N14&lt;&gt;"",OR(NOT(ISNUMBER(N14)),N14&lt;0,E14="",NOT(ISNUMBER(I14)),I14&lt;=0,I14&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C14="",H14="",N14="",OR(Z14&lt;=0,AND(AB14&lt;&gt;"",G14&lt;&gt;AB14))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C14="",H14="",N14="",I14&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C14="",H14="",N14="",AA14&gt;0,AA14&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G14" s="16"/>
+      <c r="G14" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H14" s="16"/>
       <c r="I14" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J14" s="14" t="str">
-        <f aca="false">IFERROR(IF(C14&lt;&gt;"",C14,IF(AND(H14&gt;0,ISNUMBER(H14)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H14)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C14&lt;&gt;"",C14,IF(H14&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H14)^2,IF(ISNUMBER(O14),O14*Beregning!$B$25*(Trykkberegning!$E$12/Q14)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K14" s="27" t="str">
@@ -12149,14 +13672,68 @@
         <v/>
       </c>
       <c r="L14" s="27" t="str">
-        <f aca="false">IF(C14&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C14&lt;&gt;"","Eget trykkfall",IF(H14&lt;&gt;"","Dokumentert Kv",IF(N14&lt;&gt;"","Eget K",IF(Z14&lt;=0,"Ingen generell modell",IF(A14="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N14" s="42"/>
+      <c r="O14" s="35" t="str">
+        <f aca="false">IFERROR(IF(C14&lt;&gt;"","",IF(H14&lt;&gt;"",200*(3600*PI()*(Q14/1000)^2/4/H14)^2,IF(N14&lt;&gt;"",N14,IF(Z14&gt;0,Z14*Y14,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="14" t="n">
+        <f aca="false">IF(P14="",Trykkberegning!$E$12,P14)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R14" s="14" t="str">
+        <f aca="false">IFERROR(IF(O14&gt;0,3600*PI()*(Q14/1000)^2/4*SQRT(200/O14),""),"")</f>
+        <v/>
+      </c>
+      <c r="S14" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q14/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q14/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T14" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q14/1000)^(-1.0112))/3.7+2.51/((7500000*(Q14/1000))*SQRT(S14))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U14" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q14/1000)^(-1.0112))/3.7+2.51/((7500000*(Q14/1000))*SQRT(T14))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V14" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q14/1000)^(-1.0112))/3.7+2.51/((7500000*(Q14/1000))*SQRT(U14))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W14" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q14/1000)^(-1.0112))/3.7+2.51/((7500000*(Q14/1000))*SQRT(V14))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X14" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q14/1000)^(-1.0112))/3.7+2.51/((7500000*(Q14/1000))*SQRT(W14))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y14" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q14/1000)^(-1.0112))/3.7+2.51/((7500000*(Q14/1000))*SQRT(X14))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z14" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A14&amp;"|"&amp;G14,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA14" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q14,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB14" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q14-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
       <c r="B15" s="18" t="n">
         <v>0</v>
@@ -12168,16 +13745,19 @@
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B15="",B15=0),"Ikke med",IF(OR(NOT(ISNUMBER(B15)),B15&lt;0,B15&lt;&gt;INT(B15)),"FEIL: antall",IF(A15="","FEIL: angi ventil",IF(AND(C15&lt;&gt;"",OR(NOT(ISNUMBER(C15)),C15&lt;0)),"FEIL: trykkfall",IF(AND(C15="",OR(NOT(ISNUMBER(H15)),H15&lt;=0,G15="",NOT(ISNUMBER(I15)),I15&lt;=0,I15&gt;100,E15="",M15&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B15="",B15=0),"Ikke med",IF(OR(NOT(ISNUMBER(B15)),B15&lt;0,B15&lt;&gt;INT(B15)),"FEIL: antall",IF(A15="","FEIL: angi ventil",IF(AND(C15&lt;&gt;"",OR(NOT(ISNUMBER(C15)),C15&lt;0)),"FEIL: trykkfall",IF(AND(C15="",H15&lt;&gt;"",OR(NOT(ISNUMBER(H15)),H15&lt;=0,G15="",NOT(ISNUMBER(I15)),I15&lt;=0,I15&gt;100,E15="",M15&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C15="",H15="",OR(NOT(ISNUMBER(Q15)),Q15&lt;=0)),"FEIL: lokal ID",IF(AND(C15="",H15="",ABS(Q15-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q15)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C15="",H15="",N15&lt;&gt;"",OR(NOT(ISNUMBER(N15)),N15&lt;0,E15="",NOT(ISNUMBER(I15)),I15&lt;=0,I15&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C15="",H15="",N15="",OR(Z15&lt;=0,AND(AB15&lt;&gt;"",G15&lt;&gt;AB15))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C15="",H15="",N15="",I15&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C15="",H15="",N15="",AA15&gt;0,AA15&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G15" s="16"/>
+      <c r="G15" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H15" s="16"/>
       <c r="I15" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J15" s="14" t="str">
-        <f aca="false">IFERROR(IF(C15&lt;&gt;"",C15,IF(AND(H15&gt;0,ISNUMBER(H15)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H15)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C15&lt;&gt;"",C15,IF(H15&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H15)^2,IF(ISNUMBER(O15),O15*Beregning!$B$25*(Trykkberegning!$E$12/Q15)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K15" s="27" t="str">
@@ -12185,14 +13765,68 @@
         <v/>
       </c>
       <c r="L15" s="27" t="str">
-        <f aca="false">IF(C15&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C15&lt;&gt;"","Eget trykkfall",IF(H15&lt;&gt;"","Dokumentert Kv",IF(N15&lt;&gt;"","Eget K",IF(Z15&lt;=0,"Ingen generell modell",IF(A15="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N15" s="42"/>
+      <c r="O15" s="35" t="str">
+        <f aca="false">IFERROR(IF(C15&lt;&gt;"","",IF(H15&lt;&gt;"",200*(3600*PI()*(Q15/1000)^2/4/H15)^2,IF(N15&lt;&gt;"",N15,IF(Z15&gt;0,Z15*Y15,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="14" t="n">
+        <f aca="false">IF(P15="",Trykkberegning!$E$12,P15)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R15" s="14" t="str">
+        <f aca="false">IFERROR(IF(O15&gt;0,3600*PI()*(Q15/1000)^2/4*SQRT(200/O15),""),"")</f>
+        <v/>
+      </c>
+      <c r="S15" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q15/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q15/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T15" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q15/1000)^(-1.0112))/3.7+2.51/((7500000*(Q15/1000))*SQRT(S15))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U15" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q15/1000)^(-1.0112))/3.7+2.51/((7500000*(Q15/1000))*SQRT(T15))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V15" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q15/1000)^(-1.0112))/3.7+2.51/((7500000*(Q15/1000))*SQRT(U15))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W15" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q15/1000)^(-1.0112))/3.7+2.51/((7500000*(Q15/1000))*SQRT(V15))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X15" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q15/1000)^(-1.0112))/3.7+2.51/((7500000*(Q15/1000))*SQRT(W15))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y15" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q15/1000)^(-1.0112))/3.7+2.51/((7500000*(Q15/1000))*SQRT(X15))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z15" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A15&amp;"|"&amp;G15,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA15" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q15,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB15" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q15-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6"/>
       <c r="B16" s="18" t="n">
         <v>0</v>
@@ -12204,16 +13838,19 @@
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B16="",B16=0),"Ikke med",IF(OR(NOT(ISNUMBER(B16)),B16&lt;0,B16&lt;&gt;INT(B16)),"FEIL: antall",IF(A16="","FEIL: angi ventil",IF(AND(C16&lt;&gt;"",OR(NOT(ISNUMBER(C16)),C16&lt;0)),"FEIL: trykkfall",IF(AND(C16="",OR(NOT(ISNUMBER(H16)),H16&lt;=0,G16="",NOT(ISNUMBER(I16)),I16&lt;=0,I16&gt;100,E16="",M16&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B16="",B16=0),"Ikke med",IF(OR(NOT(ISNUMBER(B16)),B16&lt;0,B16&lt;&gt;INT(B16)),"FEIL: antall",IF(A16="","FEIL: angi ventil",IF(AND(C16&lt;&gt;"",OR(NOT(ISNUMBER(C16)),C16&lt;0)),"FEIL: trykkfall",IF(AND(C16="",H16&lt;&gt;"",OR(NOT(ISNUMBER(H16)),H16&lt;=0,G16="",NOT(ISNUMBER(I16)),I16&lt;=0,I16&gt;100,E16="",M16&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C16="",H16="",OR(NOT(ISNUMBER(Q16)),Q16&lt;=0)),"FEIL: lokal ID",IF(AND(C16="",H16="",ABS(Q16-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q16)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C16="",H16="",N16&lt;&gt;"",OR(NOT(ISNUMBER(N16)),N16&lt;0,E16="",NOT(ISNUMBER(I16)),I16&lt;=0,I16&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C16="",H16="",N16="",OR(Z16&lt;=0,AND(AB16&lt;&gt;"",G16&lt;&gt;AB16))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C16="",H16="",N16="",I16&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C16="",H16="",N16="",AA16&gt;0,AA16&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G16" s="16"/>
+      <c r="G16" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H16" s="16"/>
       <c r="I16" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J16" s="14" t="str">
-        <f aca="false">IFERROR(IF(C16&lt;&gt;"",C16,IF(AND(H16&gt;0,ISNUMBER(H16)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H16)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C16&lt;&gt;"",C16,IF(H16&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H16)^2,IF(ISNUMBER(O16),O16*Beregning!$B$25*(Trykkberegning!$E$12/Q16)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K16" s="27" t="str">
@@ -12221,14 +13858,68 @@
         <v/>
       </c>
       <c r="L16" s="27" t="str">
-        <f aca="false">IF(C16&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C16&lt;&gt;"","Eget trykkfall",IF(H16&lt;&gt;"","Dokumentert Kv",IF(N16&lt;&gt;"","Eget K",IF(Z16&lt;=0,"Ingen generell modell",IF(A16="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N16" s="42"/>
+      <c r="O16" s="35" t="str">
+        <f aca="false">IFERROR(IF(C16&lt;&gt;"","",IF(H16&lt;&gt;"",200*(3600*PI()*(Q16/1000)^2/4/H16)^2,IF(N16&lt;&gt;"",N16,IF(Z16&gt;0,Z16*Y16,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="14" t="n">
+        <f aca="false">IF(P16="",Trykkberegning!$E$12,P16)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R16" s="14" t="str">
+        <f aca="false">IFERROR(IF(O16&gt;0,3600*PI()*(Q16/1000)^2/4*SQRT(200/O16),""),"")</f>
+        <v/>
+      </c>
+      <c r="S16" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q16/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q16/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T16" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q16/1000)^(-1.0112))/3.7+2.51/((7500000*(Q16/1000))*SQRT(S16))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U16" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q16/1000)^(-1.0112))/3.7+2.51/((7500000*(Q16/1000))*SQRT(T16))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V16" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q16/1000)^(-1.0112))/3.7+2.51/((7500000*(Q16/1000))*SQRT(U16))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W16" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q16/1000)^(-1.0112))/3.7+2.51/((7500000*(Q16/1000))*SQRT(V16))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X16" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q16/1000)^(-1.0112))/3.7+2.51/((7500000*(Q16/1000))*SQRT(W16))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y16" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q16/1000)^(-1.0112))/3.7+2.51/((7500000*(Q16/1000))*SQRT(X16))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z16" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A16&amp;"|"&amp;G16,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q16,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB16" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q16-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
       <c r="B17" s="18" t="n">
         <v>0</v>
@@ -12240,16 +13931,19 @@
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B17="",B17=0),"Ikke med",IF(OR(NOT(ISNUMBER(B17)),B17&lt;0,B17&lt;&gt;INT(B17)),"FEIL: antall",IF(A17="","FEIL: angi ventil",IF(AND(C17&lt;&gt;"",OR(NOT(ISNUMBER(C17)),C17&lt;0)),"FEIL: trykkfall",IF(AND(C17="",OR(NOT(ISNUMBER(H17)),H17&lt;=0,G17="",NOT(ISNUMBER(I17)),I17&lt;=0,I17&gt;100,E17="",M17&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B17="",B17=0),"Ikke med",IF(OR(NOT(ISNUMBER(B17)),B17&lt;0,B17&lt;&gt;INT(B17)),"FEIL: antall",IF(A17="","FEIL: angi ventil",IF(AND(C17&lt;&gt;"",OR(NOT(ISNUMBER(C17)),C17&lt;0)),"FEIL: trykkfall",IF(AND(C17="",H17&lt;&gt;"",OR(NOT(ISNUMBER(H17)),H17&lt;=0,G17="",NOT(ISNUMBER(I17)),I17&lt;=0,I17&gt;100,E17="",M17&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C17="",H17="",OR(NOT(ISNUMBER(Q17)),Q17&lt;=0)),"FEIL: lokal ID",IF(AND(C17="",H17="",ABS(Q17-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q17)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C17="",H17="",N17&lt;&gt;"",OR(NOT(ISNUMBER(N17)),N17&lt;0,E17="",NOT(ISNUMBER(I17)),I17&lt;=0,I17&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C17="",H17="",N17="",OR(Z17&lt;=0,AND(AB17&lt;&gt;"",G17&lt;&gt;AB17))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C17="",H17="",N17="",I17&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C17="",H17="",N17="",AA17&gt;0,AA17&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G17" s="16"/>
+      <c r="G17" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H17" s="16"/>
       <c r="I17" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J17" s="14" t="str">
-        <f aca="false">IFERROR(IF(C17&lt;&gt;"",C17,IF(AND(H17&gt;0,ISNUMBER(H17)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H17)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C17&lt;&gt;"",C17,IF(H17&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H17)^2,IF(ISNUMBER(O17),O17*Beregning!$B$25*(Trykkberegning!$E$12/Q17)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K17" s="27" t="str">
@@ -12257,14 +13951,68 @@
         <v/>
       </c>
       <c r="L17" s="27" t="str">
-        <f aca="false">IF(C17&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C17&lt;&gt;"","Eget trykkfall",IF(H17&lt;&gt;"","Dokumentert Kv",IF(N17&lt;&gt;"","Eget K",IF(Z17&lt;=0,"Ingen generell modell",IF(A17="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N17" s="42"/>
+      <c r="O17" s="35" t="str">
+        <f aca="false">IFERROR(IF(C17&lt;&gt;"","",IF(H17&lt;&gt;"",200*(3600*PI()*(Q17/1000)^2/4/H17)^2,IF(N17&lt;&gt;"",N17,IF(Z17&gt;0,Z17*Y17,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="14" t="n">
+        <f aca="false">IF(P17="",Trykkberegning!$E$12,P17)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R17" s="14" t="str">
+        <f aca="false">IFERROR(IF(O17&gt;0,3600*PI()*(Q17/1000)^2/4*SQRT(200/O17),""),"")</f>
+        <v/>
+      </c>
+      <c r="S17" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q17/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q17/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T17" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q17/1000)^(-1.0112))/3.7+2.51/((7500000*(Q17/1000))*SQRT(S17))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U17" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q17/1000)^(-1.0112))/3.7+2.51/((7500000*(Q17/1000))*SQRT(T17))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V17" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q17/1000)^(-1.0112))/3.7+2.51/((7500000*(Q17/1000))*SQRT(U17))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W17" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q17/1000)^(-1.0112))/3.7+2.51/((7500000*(Q17/1000))*SQRT(V17))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X17" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q17/1000)^(-1.0112))/3.7+2.51/((7500000*(Q17/1000))*SQRT(W17))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y17" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q17/1000)^(-1.0112))/3.7+2.51/((7500000*(Q17/1000))*SQRT(X17))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z17" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A17&amp;"|"&amp;G17,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q17,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB17" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q17-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
       <c r="B18" s="18" t="n">
         <v>0</v>
@@ -12276,16 +14024,19 @@
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B18="",B18=0),"Ikke med",IF(OR(NOT(ISNUMBER(B18)),B18&lt;0,B18&lt;&gt;INT(B18)),"FEIL: antall",IF(A18="","FEIL: angi ventil",IF(AND(C18&lt;&gt;"",OR(NOT(ISNUMBER(C18)),C18&lt;0)),"FEIL: trykkfall",IF(AND(C18="",OR(NOT(ISNUMBER(H18)),H18&lt;=0,G18="",NOT(ISNUMBER(I18)),I18&lt;=0,I18&gt;100,E18="",M18&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B18="",B18=0),"Ikke med",IF(OR(NOT(ISNUMBER(B18)),B18&lt;0,B18&lt;&gt;INT(B18)),"FEIL: antall",IF(A18="","FEIL: angi ventil",IF(AND(C18&lt;&gt;"",OR(NOT(ISNUMBER(C18)),C18&lt;0)),"FEIL: trykkfall",IF(AND(C18="",H18&lt;&gt;"",OR(NOT(ISNUMBER(H18)),H18&lt;=0,G18="",NOT(ISNUMBER(I18)),I18&lt;=0,I18&gt;100,E18="",M18&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C18="",H18="",OR(NOT(ISNUMBER(Q18)),Q18&lt;=0)),"FEIL: lokal ID",IF(AND(C18="",H18="",ABS(Q18-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q18)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C18="",H18="",N18&lt;&gt;"",OR(NOT(ISNUMBER(N18)),N18&lt;0,E18="",NOT(ISNUMBER(I18)),I18&lt;=0,I18&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C18="",H18="",N18="",OR(Z18&lt;=0,AND(AB18&lt;&gt;"",G18&lt;&gt;AB18))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C18="",H18="",N18="",I18&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C18="",H18="",N18="",AA18&gt;0,AA18&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G18" s="16"/>
+      <c r="G18" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H18" s="16"/>
       <c r="I18" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J18" s="14" t="str">
-        <f aca="false">IFERROR(IF(C18&lt;&gt;"",C18,IF(AND(H18&gt;0,ISNUMBER(H18)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H18)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C18&lt;&gt;"",C18,IF(H18&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H18)^2,IF(ISNUMBER(O18),O18*Beregning!$B$25*(Trykkberegning!$E$12/Q18)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K18" s="27" t="str">
@@ -12293,14 +14044,68 @@
         <v/>
       </c>
       <c r="L18" s="27" t="str">
-        <f aca="false">IF(C18&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C18&lt;&gt;"","Eget trykkfall",IF(H18&lt;&gt;"","Dokumentert Kv",IF(N18&lt;&gt;"","Eget K",IF(Z18&lt;=0,"Ingen generell modell",IF(A18="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N18" s="42"/>
+      <c r="O18" s="35" t="str">
+        <f aca="false">IFERROR(IF(C18&lt;&gt;"","",IF(H18&lt;&gt;"",200*(3600*PI()*(Q18/1000)^2/4/H18)^2,IF(N18&lt;&gt;"",N18,IF(Z18&gt;0,Z18*Y18,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="14" t="n">
+        <f aca="false">IF(P18="",Trykkberegning!$E$12,P18)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R18" s="14" t="str">
+        <f aca="false">IFERROR(IF(O18&gt;0,3600*PI()*(Q18/1000)^2/4*SQRT(200/O18),""),"")</f>
+        <v/>
+      </c>
+      <c r="S18" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q18/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q18/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T18" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q18/1000)^(-1.0112))/3.7+2.51/((7500000*(Q18/1000))*SQRT(S18))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U18" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q18/1000)^(-1.0112))/3.7+2.51/((7500000*(Q18/1000))*SQRT(T18))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V18" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q18/1000)^(-1.0112))/3.7+2.51/((7500000*(Q18/1000))*SQRT(U18))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W18" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q18/1000)^(-1.0112))/3.7+2.51/((7500000*(Q18/1000))*SQRT(V18))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X18" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q18/1000)^(-1.0112))/3.7+2.51/((7500000*(Q18/1000))*SQRT(W18))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y18" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q18/1000)^(-1.0112))/3.7+2.51/((7500000*(Q18/1000))*SQRT(X18))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z18" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A18&amp;"|"&amp;G18,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q18,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB18" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q18-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
       <c r="B19" s="18" t="n">
         <v>0</v>
@@ -12312,16 +14117,19 @@
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B19="",B19=0),"Ikke med",IF(OR(NOT(ISNUMBER(B19)),B19&lt;0,B19&lt;&gt;INT(B19)),"FEIL: antall",IF(A19="","FEIL: angi ventil",IF(AND(C19&lt;&gt;"",OR(NOT(ISNUMBER(C19)),C19&lt;0)),"FEIL: trykkfall",IF(AND(C19="",OR(NOT(ISNUMBER(H19)),H19&lt;=0,G19="",NOT(ISNUMBER(I19)),I19&lt;=0,I19&gt;100,E19="",M19&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B19="",B19=0),"Ikke med",IF(OR(NOT(ISNUMBER(B19)),B19&lt;0,B19&lt;&gt;INT(B19)),"FEIL: antall",IF(A19="","FEIL: angi ventil",IF(AND(C19&lt;&gt;"",OR(NOT(ISNUMBER(C19)),C19&lt;0)),"FEIL: trykkfall",IF(AND(C19="",H19&lt;&gt;"",OR(NOT(ISNUMBER(H19)),H19&lt;=0,G19="",NOT(ISNUMBER(I19)),I19&lt;=0,I19&gt;100,E19="",M19&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C19="",H19="",OR(NOT(ISNUMBER(Q19)),Q19&lt;=0)),"FEIL: lokal ID",IF(AND(C19="",H19="",ABS(Q19-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q19)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C19="",H19="",N19&lt;&gt;"",OR(NOT(ISNUMBER(N19)),N19&lt;0,E19="",NOT(ISNUMBER(I19)),I19&lt;=0,I19&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C19="",H19="",N19="",OR(Z19&lt;=0,AND(AB19&lt;&gt;"",G19&lt;&gt;AB19))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C19="",H19="",N19="",I19&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C19="",H19="",N19="",AA19&gt;0,AA19&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G19" s="16"/>
+      <c r="G19" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H19" s="16"/>
       <c r="I19" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J19" s="14" t="str">
-        <f aca="false">IFERROR(IF(C19&lt;&gt;"",C19,IF(AND(H19&gt;0,ISNUMBER(H19)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H19)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C19&lt;&gt;"",C19,IF(H19&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H19)^2,IF(ISNUMBER(O19),O19*Beregning!$B$25*(Trykkberegning!$E$12/Q19)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K19" s="27" t="str">
@@ -12329,14 +14137,68 @@
         <v/>
       </c>
       <c r="L19" s="27" t="str">
-        <f aca="false">IF(C19&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C19&lt;&gt;"","Eget trykkfall",IF(H19&lt;&gt;"","Dokumentert Kv",IF(N19&lt;&gt;"","Eget K",IF(Z19&lt;=0,"Ingen generell modell",IF(A19="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N19" s="42"/>
+      <c r="O19" s="35" t="str">
+        <f aca="false">IFERROR(IF(C19&lt;&gt;"","",IF(H19&lt;&gt;"",200*(3600*PI()*(Q19/1000)^2/4/H19)^2,IF(N19&lt;&gt;"",N19,IF(Z19&gt;0,Z19*Y19,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="14" t="n">
+        <f aca="false">IF(P19="",Trykkberegning!$E$12,P19)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R19" s="14" t="str">
+        <f aca="false">IFERROR(IF(O19&gt;0,3600*PI()*(Q19/1000)^2/4*SQRT(200/O19),""),"")</f>
+        <v/>
+      </c>
+      <c r="S19" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q19/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q19/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T19" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q19/1000)^(-1.0112))/3.7+2.51/((7500000*(Q19/1000))*SQRT(S19))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U19" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q19/1000)^(-1.0112))/3.7+2.51/((7500000*(Q19/1000))*SQRT(T19))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V19" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q19/1000)^(-1.0112))/3.7+2.51/((7500000*(Q19/1000))*SQRT(U19))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W19" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q19/1000)^(-1.0112))/3.7+2.51/((7500000*(Q19/1000))*SQRT(V19))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X19" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q19/1000)^(-1.0112))/3.7+2.51/((7500000*(Q19/1000))*SQRT(W19))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y19" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q19/1000)^(-1.0112))/3.7+2.51/((7500000*(Q19/1000))*SQRT(X19))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z19" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A19&amp;"|"&amp;G19,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q19,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB19" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q19-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6"/>
       <c r="B20" s="18" t="n">
         <v>0</v>
@@ -12348,16 +14210,19 @@
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B20="",B20=0),"Ikke med",IF(OR(NOT(ISNUMBER(B20)),B20&lt;0,B20&lt;&gt;INT(B20)),"FEIL: antall",IF(A20="","FEIL: angi ventil",IF(AND(C20&lt;&gt;"",OR(NOT(ISNUMBER(C20)),C20&lt;0)),"FEIL: trykkfall",IF(AND(C20="",OR(NOT(ISNUMBER(H20)),H20&lt;=0,G20="",NOT(ISNUMBER(I20)),I20&lt;=0,I20&gt;100,E20="",M20&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B20="",B20=0),"Ikke med",IF(OR(NOT(ISNUMBER(B20)),B20&lt;0,B20&lt;&gt;INT(B20)),"FEIL: antall",IF(A20="","FEIL: angi ventil",IF(AND(C20&lt;&gt;"",OR(NOT(ISNUMBER(C20)),C20&lt;0)),"FEIL: trykkfall",IF(AND(C20="",H20&lt;&gt;"",OR(NOT(ISNUMBER(H20)),H20&lt;=0,G20="",NOT(ISNUMBER(I20)),I20&lt;=0,I20&gt;100,E20="",M20&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C20="",H20="",OR(NOT(ISNUMBER(Q20)),Q20&lt;=0)),"FEIL: lokal ID",IF(AND(C20="",H20="",ABS(Q20-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q20)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C20="",H20="",N20&lt;&gt;"",OR(NOT(ISNUMBER(N20)),N20&lt;0,E20="",NOT(ISNUMBER(I20)),I20&lt;=0,I20&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C20="",H20="",N20="",OR(Z20&lt;=0,AND(AB20&lt;&gt;"",G20&lt;&gt;AB20))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C20="",H20="",N20="",I20&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C20="",H20="",N20="",AA20&gt;0,AA20&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G20" s="16"/>
+      <c r="G20" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H20" s="16"/>
       <c r="I20" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J20" s="14" t="str">
-        <f aca="false">IFERROR(IF(C20&lt;&gt;"",C20,IF(AND(H20&gt;0,ISNUMBER(H20)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H20)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C20&lt;&gt;"",C20,IF(H20&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H20)^2,IF(ISNUMBER(O20),O20*Beregning!$B$25*(Trykkberegning!$E$12/Q20)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K20" s="27" t="str">
@@ -12365,14 +14230,68 @@
         <v/>
       </c>
       <c r="L20" s="27" t="str">
-        <f aca="false">IF(C20&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C20&lt;&gt;"","Eget trykkfall",IF(H20&lt;&gt;"","Dokumentert Kv",IF(N20&lt;&gt;"","Eget K",IF(Z20&lt;=0,"Ingen generell modell",IF(A20="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M20" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N20" s="42"/>
+      <c r="O20" s="35" t="str">
+        <f aca="false">IFERROR(IF(C20&lt;&gt;"","",IF(H20&lt;&gt;"",200*(3600*PI()*(Q20/1000)^2/4/H20)^2,IF(N20&lt;&gt;"",N20,IF(Z20&gt;0,Z20*Y20,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="14" t="n">
+        <f aca="false">IF(P20="",Trykkberegning!$E$12,P20)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R20" s="14" t="str">
+        <f aca="false">IFERROR(IF(O20&gt;0,3600*PI()*(Q20/1000)^2/4*SQRT(200/O20),""),"")</f>
+        <v/>
+      </c>
+      <c r="S20" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q20/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q20/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T20" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q20/1000)^(-1.0112))/3.7+2.51/((7500000*(Q20/1000))*SQRT(S20))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U20" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q20/1000)^(-1.0112))/3.7+2.51/((7500000*(Q20/1000))*SQRT(T20))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V20" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q20/1000)^(-1.0112))/3.7+2.51/((7500000*(Q20/1000))*SQRT(U20))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W20" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q20/1000)^(-1.0112))/3.7+2.51/((7500000*(Q20/1000))*SQRT(V20))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X20" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q20/1000)^(-1.0112))/3.7+2.51/((7500000*(Q20/1000))*SQRT(W20))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y20" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q20/1000)^(-1.0112))/3.7+2.51/((7500000*(Q20/1000))*SQRT(X20))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z20" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A20&amp;"|"&amp;G20,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA20" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q20,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB20" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q20-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6"/>
       <c r="B21" s="18" t="n">
         <v>0</v>
@@ -12384,16 +14303,19 @@
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B21="",B21=0),"Ikke med",IF(OR(NOT(ISNUMBER(B21)),B21&lt;0,B21&lt;&gt;INT(B21)),"FEIL: antall",IF(A21="","FEIL: angi ventil",IF(AND(C21&lt;&gt;"",OR(NOT(ISNUMBER(C21)),C21&lt;0)),"FEIL: trykkfall",IF(AND(C21="",OR(NOT(ISNUMBER(H21)),H21&lt;=0,G21="",NOT(ISNUMBER(I21)),I21&lt;=0,I21&gt;100,E21="",M21&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B21="",B21=0),"Ikke med",IF(OR(NOT(ISNUMBER(B21)),B21&lt;0,B21&lt;&gt;INT(B21)),"FEIL: antall",IF(A21="","FEIL: angi ventil",IF(AND(C21&lt;&gt;"",OR(NOT(ISNUMBER(C21)),C21&lt;0)),"FEIL: trykkfall",IF(AND(C21="",H21&lt;&gt;"",OR(NOT(ISNUMBER(H21)),H21&lt;=0,G21="",NOT(ISNUMBER(I21)),I21&lt;=0,I21&gt;100,E21="",M21&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C21="",H21="",OR(NOT(ISNUMBER(Q21)),Q21&lt;=0)),"FEIL: lokal ID",IF(AND(C21="",H21="",ABS(Q21-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q21)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C21="",H21="",N21&lt;&gt;"",OR(NOT(ISNUMBER(N21)),N21&lt;0,E21="",NOT(ISNUMBER(I21)),I21&lt;=0,I21&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C21="",H21="",N21="",OR(Z21&lt;=0,AND(AB21&lt;&gt;"",G21&lt;&gt;AB21))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C21="",H21="",N21="",I21&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C21="",H21="",N21="",AA21&gt;0,AA21&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G21" s="16"/>
+      <c r="G21" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H21" s="16"/>
       <c r="I21" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J21" s="14" t="str">
-        <f aca="false">IFERROR(IF(C21&lt;&gt;"",C21,IF(AND(H21&gt;0,ISNUMBER(H21)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H21)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C21&lt;&gt;"",C21,IF(H21&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H21)^2,IF(ISNUMBER(O21),O21*Beregning!$B$25*(Trykkberegning!$E$12/Q21)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K21" s="27" t="str">
@@ -12401,14 +14323,68 @@
         <v/>
       </c>
       <c r="L21" s="27" t="str">
-        <f aca="false">IF(C21&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C21&lt;&gt;"","Eget trykkfall",IF(H21&lt;&gt;"","Dokumentert Kv",IF(N21&lt;&gt;"","Eget K",IF(Z21&lt;=0,"Ingen generell modell",IF(A21="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M21" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N21" s="42"/>
+      <c r="O21" s="35" t="str">
+        <f aca="false">IFERROR(IF(C21&lt;&gt;"","",IF(H21&lt;&gt;"",200*(3600*PI()*(Q21/1000)^2/4/H21)^2,IF(N21&lt;&gt;"",N21,IF(Z21&gt;0,Z21*Y21,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="14" t="n">
+        <f aca="false">IF(P21="",Trykkberegning!$E$12,P21)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R21" s="14" t="str">
+        <f aca="false">IFERROR(IF(O21&gt;0,3600*PI()*(Q21/1000)^2/4*SQRT(200/O21),""),"")</f>
+        <v/>
+      </c>
+      <c r="S21" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q21/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q21/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T21" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q21/1000)^(-1.0112))/3.7+2.51/((7500000*(Q21/1000))*SQRT(S21))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U21" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q21/1000)^(-1.0112))/3.7+2.51/((7500000*(Q21/1000))*SQRT(T21))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V21" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q21/1000)^(-1.0112))/3.7+2.51/((7500000*(Q21/1000))*SQRT(U21))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W21" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q21/1000)^(-1.0112))/3.7+2.51/((7500000*(Q21/1000))*SQRT(V21))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X21" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q21/1000)^(-1.0112))/3.7+2.51/((7500000*(Q21/1000))*SQRT(W21))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y21" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q21/1000)^(-1.0112))/3.7+2.51/((7500000*(Q21/1000))*SQRT(X21))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z21" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A21&amp;"|"&amp;G21,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q21,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB21" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q21-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6"/>
       <c r="B22" s="18" t="n">
         <v>0</v>
@@ -12420,16 +14396,19 @@
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B22="",B22=0),"Ikke med",IF(OR(NOT(ISNUMBER(B22)),B22&lt;0,B22&lt;&gt;INT(B22)),"FEIL: antall",IF(A22="","FEIL: angi ventil",IF(AND(C22&lt;&gt;"",OR(NOT(ISNUMBER(C22)),C22&lt;0)),"FEIL: trykkfall",IF(AND(C22="",OR(NOT(ISNUMBER(H22)),H22&lt;=0,G22="",NOT(ISNUMBER(I22)),I22&lt;=0,I22&gt;100,E22="",M22&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B22="",B22=0),"Ikke med",IF(OR(NOT(ISNUMBER(B22)),B22&lt;0,B22&lt;&gt;INT(B22)),"FEIL: antall",IF(A22="","FEIL: angi ventil",IF(AND(C22&lt;&gt;"",OR(NOT(ISNUMBER(C22)),C22&lt;0)),"FEIL: trykkfall",IF(AND(C22="",H22&lt;&gt;"",OR(NOT(ISNUMBER(H22)),H22&lt;=0,G22="",NOT(ISNUMBER(I22)),I22&lt;=0,I22&gt;100,E22="",M22&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C22="",H22="",OR(NOT(ISNUMBER(Q22)),Q22&lt;=0)),"FEIL: lokal ID",IF(AND(C22="",H22="",ABS(Q22-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q22)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C22="",H22="",N22&lt;&gt;"",OR(NOT(ISNUMBER(N22)),N22&lt;0,E22="",NOT(ISNUMBER(I22)),I22&lt;=0,I22&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C22="",H22="",N22="",OR(Z22&lt;=0,AND(AB22&lt;&gt;"",G22&lt;&gt;AB22))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C22="",H22="",N22="",I22&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C22="",H22="",N22="",AA22&gt;0,AA22&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G22" s="16"/>
+      <c r="G22" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H22" s="16"/>
       <c r="I22" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J22" s="14" t="str">
-        <f aca="false">IFERROR(IF(C22&lt;&gt;"",C22,IF(AND(H22&gt;0,ISNUMBER(H22)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H22)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C22&lt;&gt;"",C22,IF(H22&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H22)^2,IF(ISNUMBER(O22),O22*Beregning!$B$25*(Trykkberegning!$E$12/Q22)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K22" s="27" t="str">
@@ -12437,14 +14416,68 @@
         <v/>
       </c>
       <c r="L22" s="27" t="str">
-        <f aca="false">IF(C22&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C22&lt;&gt;"","Eget trykkfall",IF(H22&lt;&gt;"","Dokumentert Kv",IF(N22&lt;&gt;"","Eget K",IF(Z22&lt;=0,"Ingen generell modell",IF(A22="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M22" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N22" s="42"/>
+      <c r="O22" s="35" t="str">
+        <f aca="false">IFERROR(IF(C22&lt;&gt;"","",IF(H22&lt;&gt;"",200*(3600*PI()*(Q22/1000)^2/4/H22)^2,IF(N22&lt;&gt;"",N22,IF(Z22&gt;0,Z22*Y22,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="14" t="n">
+        <f aca="false">IF(P22="",Trykkberegning!$E$12,P22)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R22" s="14" t="str">
+        <f aca="false">IFERROR(IF(O22&gt;0,3600*PI()*(Q22/1000)^2/4*SQRT(200/O22),""),"")</f>
+        <v/>
+      </c>
+      <c r="S22" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q22/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q22/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T22" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q22/1000)^(-1.0112))/3.7+2.51/((7500000*(Q22/1000))*SQRT(S22))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U22" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q22/1000)^(-1.0112))/3.7+2.51/((7500000*(Q22/1000))*SQRT(T22))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V22" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q22/1000)^(-1.0112))/3.7+2.51/((7500000*(Q22/1000))*SQRT(U22))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W22" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q22/1000)^(-1.0112))/3.7+2.51/((7500000*(Q22/1000))*SQRT(V22))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X22" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q22/1000)^(-1.0112))/3.7+2.51/((7500000*(Q22/1000))*SQRT(W22))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y22" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q22/1000)^(-1.0112))/3.7+2.51/((7500000*(Q22/1000))*SQRT(X22))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z22" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A22&amp;"|"&amp;G22,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q22,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB22" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q22-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
       <c r="B23" s="18" t="n">
         <v>0</v>
@@ -12456,16 +14489,19 @@
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B23="",B23=0),"Ikke med",IF(OR(NOT(ISNUMBER(B23)),B23&lt;0,B23&lt;&gt;INT(B23)),"FEIL: antall",IF(A23="","FEIL: angi ventil",IF(AND(C23&lt;&gt;"",OR(NOT(ISNUMBER(C23)),C23&lt;0)),"FEIL: trykkfall",IF(AND(C23="",OR(NOT(ISNUMBER(H23)),H23&lt;=0,G23="",NOT(ISNUMBER(I23)),I23&lt;=0,I23&gt;100,E23="",M23&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B23="",B23=0),"Ikke med",IF(OR(NOT(ISNUMBER(B23)),B23&lt;0,B23&lt;&gt;INT(B23)),"FEIL: antall",IF(A23="","FEIL: angi ventil",IF(AND(C23&lt;&gt;"",OR(NOT(ISNUMBER(C23)),C23&lt;0)),"FEIL: trykkfall",IF(AND(C23="",H23&lt;&gt;"",OR(NOT(ISNUMBER(H23)),H23&lt;=0,G23="",NOT(ISNUMBER(I23)),I23&lt;=0,I23&gt;100,E23="",M23&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C23="",H23="",OR(NOT(ISNUMBER(Q23)),Q23&lt;=0)),"FEIL: lokal ID",IF(AND(C23="",H23="",ABS(Q23-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q23)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C23="",H23="",N23&lt;&gt;"",OR(NOT(ISNUMBER(N23)),N23&lt;0,E23="",NOT(ISNUMBER(I23)),I23&lt;=0,I23&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C23="",H23="",N23="",OR(Z23&lt;=0,AND(AB23&lt;&gt;"",G23&lt;&gt;AB23))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C23="",H23="",N23="",I23&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C23="",H23="",N23="",AA23&gt;0,AA23&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G23" s="16"/>
+      <c r="G23" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H23" s="16"/>
       <c r="I23" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J23" s="14" t="str">
-        <f aca="false">IFERROR(IF(C23&lt;&gt;"",C23,IF(AND(H23&gt;0,ISNUMBER(H23)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H23)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C23&lt;&gt;"",C23,IF(H23&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H23)^2,IF(ISNUMBER(O23),O23*Beregning!$B$25*(Trykkberegning!$E$12/Q23)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K23" s="27" t="str">
@@ -12473,14 +14509,68 @@
         <v/>
       </c>
       <c r="L23" s="27" t="str">
-        <f aca="false">IF(C23&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C23&lt;&gt;"","Eget trykkfall",IF(H23&lt;&gt;"","Dokumentert Kv",IF(N23&lt;&gt;"","Eget K",IF(Z23&lt;=0,"Ingen generell modell",IF(A23="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M23" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N23" s="42"/>
+      <c r="O23" s="35" t="str">
+        <f aca="false">IFERROR(IF(C23&lt;&gt;"","",IF(H23&lt;&gt;"",200*(3600*PI()*(Q23/1000)^2/4/H23)^2,IF(N23&lt;&gt;"",N23,IF(Z23&gt;0,Z23*Y23,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="14" t="n">
+        <f aca="false">IF(P23="",Trykkberegning!$E$12,P23)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R23" s="14" t="str">
+        <f aca="false">IFERROR(IF(O23&gt;0,3600*PI()*(Q23/1000)^2/4*SQRT(200/O23),""),"")</f>
+        <v/>
+      </c>
+      <c r="S23" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q23/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q23/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T23" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q23/1000)^(-1.0112))/3.7+2.51/((7500000*(Q23/1000))*SQRT(S23))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U23" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q23/1000)^(-1.0112))/3.7+2.51/((7500000*(Q23/1000))*SQRT(T23))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V23" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q23/1000)^(-1.0112))/3.7+2.51/((7500000*(Q23/1000))*SQRT(U23))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W23" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q23/1000)^(-1.0112))/3.7+2.51/((7500000*(Q23/1000))*SQRT(V23))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X23" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q23/1000)^(-1.0112))/3.7+2.51/((7500000*(Q23/1000))*SQRT(W23))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y23" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q23/1000)^(-1.0112))/3.7+2.51/((7500000*(Q23/1000))*SQRT(X23))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z23" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A23&amp;"|"&amp;G23,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA23" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q23,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB23" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q23-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
       <c r="B24" s="18" t="n">
         <v>0</v>
@@ -12492,16 +14582,19 @@
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B24="",B24=0),"Ikke med",IF(OR(NOT(ISNUMBER(B24)),B24&lt;0,B24&lt;&gt;INT(B24)),"FEIL: antall",IF(A24="","FEIL: angi ventil",IF(AND(C24&lt;&gt;"",OR(NOT(ISNUMBER(C24)),C24&lt;0)),"FEIL: trykkfall",IF(AND(C24="",OR(NOT(ISNUMBER(H24)),H24&lt;=0,G24="",NOT(ISNUMBER(I24)),I24&lt;=0,I24&gt;100,E24="",M24&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B24="",B24=0),"Ikke med",IF(OR(NOT(ISNUMBER(B24)),B24&lt;0,B24&lt;&gt;INT(B24)),"FEIL: antall",IF(A24="","FEIL: angi ventil",IF(AND(C24&lt;&gt;"",OR(NOT(ISNUMBER(C24)),C24&lt;0)),"FEIL: trykkfall",IF(AND(C24="",H24&lt;&gt;"",OR(NOT(ISNUMBER(H24)),H24&lt;=0,G24="",NOT(ISNUMBER(I24)),I24&lt;=0,I24&gt;100,E24="",M24&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C24="",H24="",OR(NOT(ISNUMBER(Q24)),Q24&lt;=0)),"FEIL: lokal ID",IF(AND(C24="",H24="",ABS(Q24-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q24)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C24="",H24="",N24&lt;&gt;"",OR(NOT(ISNUMBER(N24)),N24&lt;0,E24="",NOT(ISNUMBER(I24)),I24&lt;=0,I24&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C24="",H24="",N24="",OR(Z24&lt;=0,AND(AB24&lt;&gt;"",G24&lt;&gt;AB24))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C24="",H24="",N24="",I24&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C24="",H24="",N24="",AA24&gt;0,AA24&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G24" s="16"/>
+      <c r="G24" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H24" s="16"/>
       <c r="I24" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J24" s="14" t="str">
-        <f aca="false">IFERROR(IF(C24&lt;&gt;"",C24,IF(AND(H24&gt;0,ISNUMBER(H24)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H24)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C24&lt;&gt;"",C24,IF(H24&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H24)^2,IF(ISNUMBER(O24),O24*Beregning!$B$25*(Trykkberegning!$E$12/Q24)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K24" s="27" t="str">
@@ -12509,14 +14602,68 @@
         <v/>
       </c>
       <c r="L24" s="27" t="str">
-        <f aca="false">IF(C24&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C24&lt;&gt;"","Eget trykkfall",IF(H24&lt;&gt;"","Dokumentert Kv",IF(N24&lt;&gt;"","Eget K",IF(Z24&lt;=0,"Ingen generell modell",IF(A24="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M24" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N24" s="42"/>
+      <c r="O24" s="35" t="str">
+        <f aca="false">IFERROR(IF(C24&lt;&gt;"","",IF(H24&lt;&gt;"",200*(3600*PI()*(Q24/1000)^2/4/H24)^2,IF(N24&lt;&gt;"",N24,IF(Z24&gt;0,Z24*Y24,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="14" t="n">
+        <f aca="false">IF(P24="",Trykkberegning!$E$12,P24)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R24" s="14" t="str">
+        <f aca="false">IFERROR(IF(O24&gt;0,3600*PI()*(Q24/1000)^2/4*SQRT(200/O24),""),"")</f>
+        <v/>
+      </c>
+      <c r="S24" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q24/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q24/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T24" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q24/1000)^(-1.0112))/3.7+2.51/((7500000*(Q24/1000))*SQRT(S24))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U24" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q24/1000)^(-1.0112))/3.7+2.51/((7500000*(Q24/1000))*SQRT(T24))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V24" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q24/1000)^(-1.0112))/3.7+2.51/((7500000*(Q24/1000))*SQRT(U24))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W24" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q24/1000)^(-1.0112))/3.7+2.51/((7500000*(Q24/1000))*SQRT(V24))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X24" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q24/1000)^(-1.0112))/3.7+2.51/((7500000*(Q24/1000))*SQRT(W24))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y24" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q24/1000)^(-1.0112))/3.7+2.51/((7500000*(Q24/1000))*SQRT(X24))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z24" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A24&amp;"|"&amp;G24,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA24" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q24,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB24" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q24-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6"/>
       <c r="B25" s="18" t="n">
         <v>0</v>
@@ -12528,16 +14675,19 @@
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B25="",B25=0),"Ikke med",IF(OR(NOT(ISNUMBER(B25)),B25&lt;0,B25&lt;&gt;INT(B25)),"FEIL: antall",IF(A25="","FEIL: angi ventil",IF(AND(C25&lt;&gt;"",OR(NOT(ISNUMBER(C25)),C25&lt;0)),"FEIL: trykkfall",IF(AND(C25="",OR(NOT(ISNUMBER(H25)),H25&lt;=0,G25="",NOT(ISNUMBER(I25)),I25&lt;=0,I25&gt;100,E25="",M25&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B25="",B25=0),"Ikke med",IF(OR(NOT(ISNUMBER(B25)),B25&lt;0,B25&lt;&gt;INT(B25)),"FEIL: antall",IF(A25="","FEIL: angi ventil",IF(AND(C25&lt;&gt;"",OR(NOT(ISNUMBER(C25)),C25&lt;0)),"FEIL: trykkfall",IF(AND(C25="",H25&lt;&gt;"",OR(NOT(ISNUMBER(H25)),H25&lt;=0,G25="",NOT(ISNUMBER(I25)),I25&lt;=0,I25&gt;100,E25="",M25&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C25="",H25="",OR(NOT(ISNUMBER(Q25)),Q25&lt;=0)),"FEIL: lokal ID",IF(AND(C25="",H25="",ABS(Q25-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q25)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C25="",H25="",N25&lt;&gt;"",OR(NOT(ISNUMBER(N25)),N25&lt;0,E25="",NOT(ISNUMBER(I25)),I25&lt;=0,I25&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C25="",H25="",N25="",OR(Z25&lt;=0,AND(AB25&lt;&gt;"",G25&lt;&gt;AB25))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C25="",H25="",N25="",I25&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C25="",H25="",N25="",AA25&gt;0,AA25&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G25" s="16"/>
+      <c r="G25" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H25" s="16"/>
       <c r="I25" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J25" s="14" t="str">
-        <f aca="false">IFERROR(IF(C25&lt;&gt;"",C25,IF(AND(H25&gt;0,ISNUMBER(H25)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H25)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C25&lt;&gt;"",C25,IF(H25&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H25)^2,IF(ISNUMBER(O25),O25*Beregning!$B$25*(Trykkberegning!$E$12/Q25)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K25" s="27" t="str">
@@ -12545,14 +14695,68 @@
         <v/>
       </c>
       <c r="L25" s="27" t="str">
-        <f aca="false">IF(C25&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C25&lt;&gt;"","Eget trykkfall",IF(H25&lt;&gt;"","Dokumentert Kv",IF(N25&lt;&gt;"","Eget K",IF(Z25&lt;=0,"Ingen generell modell",IF(A25="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N25" s="42"/>
+      <c r="O25" s="35" t="str">
+        <f aca="false">IFERROR(IF(C25&lt;&gt;"","",IF(H25&lt;&gt;"",200*(3600*PI()*(Q25/1000)^2/4/H25)^2,IF(N25&lt;&gt;"",N25,IF(Z25&gt;0,Z25*Y25,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="14" t="n">
+        <f aca="false">IF(P25="",Trykkberegning!$E$12,P25)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R25" s="14" t="str">
+        <f aca="false">IFERROR(IF(O25&gt;0,3600*PI()*(Q25/1000)^2/4*SQRT(200/O25),""),"")</f>
+        <v/>
+      </c>
+      <c r="S25" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q25/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q25/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T25" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q25/1000)^(-1.0112))/3.7+2.51/((7500000*(Q25/1000))*SQRT(S25))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U25" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q25/1000)^(-1.0112))/3.7+2.51/((7500000*(Q25/1000))*SQRT(T25))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V25" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q25/1000)^(-1.0112))/3.7+2.51/((7500000*(Q25/1000))*SQRT(U25))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W25" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q25/1000)^(-1.0112))/3.7+2.51/((7500000*(Q25/1000))*SQRT(V25))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X25" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q25/1000)^(-1.0112))/3.7+2.51/((7500000*(Q25/1000))*SQRT(W25))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y25" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q25/1000)^(-1.0112))/3.7+2.51/((7500000*(Q25/1000))*SQRT(X25))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z25" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A25&amp;"|"&amp;G25,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA25" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q25,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB25" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q25-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
       <c r="B26" s="18" t="n">
         <v>0</v>
@@ -12564,16 +14768,19 @@
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B26="",B26=0),"Ikke med",IF(OR(NOT(ISNUMBER(B26)),B26&lt;0,B26&lt;&gt;INT(B26)),"FEIL: antall",IF(A26="","FEIL: angi ventil",IF(AND(C26&lt;&gt;"",OR(NOT(ISNUMBER(C26)),C26&lt;0)),"FEIL: trykkfall",IF(AND(C26="",OR(NOT(ISNUMBER(H26)),H26&lt;=0,G26="",NOT(ISNUMBER(I26)),I26&lt;=0,I26&gt;100,E26="",M26&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B26="",B26=0),"Ikke med",IF(OR(NOT(ISNUMBER(B26)),B26&lt;0,B26&lt;&gt;INT(B26)),"FEIL: antall",IF(A26="","FEIL: angi ventil",IF(AND(C26&lt;&gt;"",OR(NOT(ISNUMBER(C26)),C26&lt;0)),"FEIL: trykkfall",IF(AND(C26="",H26&lt;&gt;"",OR(NOT(ISNUMBER(H26)),H26&lt;=0,G26="",NOT(ISNUMBER(I26)),I26&lt;=0,I26&gt;100,E26="",M26&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C26="",H26="",OR(NOT(ISNUMBER(Q26)),Q26&lt;=0)),"FEIL: lokal ID",IF(AND(C26="",H26="",ABS(Q26-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q26)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C26="",H26="",N26&lt;&gt;"",OR(NOT(ISNUMBER(N26)),N26&lt;0,E26="",NOT(ISNUMBER(I26)),I26&lt;=0,I26&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C26="",H26="",N26="",OR(Z26&lt;=0,AND(AB26&lt;&gt;"",G26&lt;&gt;AB26))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C26="",H26="",N26="",I26&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C26="",H26="",N26="",AA26&gt;0,AA26&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G26" s="16"/>
+      <c r="G26" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H26" s="16"/>
       <c r="I26" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J26" s="14" t="str">
-        <f aca="false">IFERROR(IF(C26&lt;&gt;"",C26,IF(AND(H26&gt;0,ISNUMBER(H26)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H26)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C26&lt;&gt;"",C26,IF(H26&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H26)^2,IF(ISNUMBER(O26),O26*Beregning!$B$25*(Trykkberegning!$E$12/Q26)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K26" s="27" t="str">
@@ -12581,14 +14788,68 @@
         <v/>
       </c>
       <c r="L26" s="27" t="str">
-        <f aca="false">IF(C26&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C26&lt;&gt;"","Eget trykkfall",IF(H26&lt;&gt;"","Dokumentert Kv",IF(N26&lt;&gt;"","Eget K",IF(Z26&lt;=0,"Ingen generell modell",IF(A26="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N26" s="42"/>
+      <c r="O26" s="35" t="str">
+        <f aca="false">IFERROR(IF(C26&lt;&gt;"","",IF(H26&lt;&gt;"",200*(3600*PI()*(Q26/1000)^2/4/H26)^2,IF(N26&lt;&gt;"",N26,IF(Z26&gt;0,Z26*Y26,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="14" t="n">
+        <f aca="false">IF(P26="",Trykkberegning!$E$12,P26)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R26" s="14" t="str">
+        <f aca="false">IFERROR(IF(O26&gt;0,3600*PI()*(Q26/1000)^2/4*SQRT(200/O26),""),"")</f>
+        <v/>
+      </c>
+      <c r="S26" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q26/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q26/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T26" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q26/1000)^(-1.0112))/3.7+2.51/((7500000*(Q26/1000))*SQRT(S26))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U26" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q26/1000)^(-1.0112))/3.7+2.51/((7500000*(Q26/1000))*SQRT(T26))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V26" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q26/1000)^(-1.0112))/3.7+2.51/((7500000*(Q26/1000))*SQRT(U26))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W26" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q26/1000)^(-1.0112))/3.7+2.51/((7500000*(Q26/1000))*SQRT(V26))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X26" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q26/1000)^(-1.0112))/3.7+2.51/((7500000*(Q26/1000))*SQRT(W26))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y26" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q26/1000)^(-1.0112))/3.7+2.51/((7500000*(Q26/1000))*SQRT(X26))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z26" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A26&amp;"|"&amp;G26,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA26" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q26,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB26" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q26-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6"/>
       <c r="B27" s="18" t="n">
         <v>0</v>
@@ -12600,16 +14861,19 @@
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B27="",B27=0),"Ikke med",IF(OR(NOT(ISNUMBER(B27)),B27&lt;0,B27&lt;&gt;INT(B27)),"FEIL: antall",IF(A27="","FEIL: angi ventil",IF(AND(C27&lt;&gt;"",OR(NOT(ISNUMBER(C27)),C27&lt;0)),"FEIL: trykkfall",IF(AND(C27="",OR(NOT(ISNUMBER(H27)),H27&lt;=0,G27="",NOT(ISNUMBER(I27)),I27&lt;=0,I27&gt;100,E27="",M27&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B27="",B27=0),"Ikke med",IF(OR(NOT(ISNUMBER(B27)),B27&lt;0,B27&lt;&gt;INT(B27)),"FEIL: antall",IF(A27="","FEIL: angi ventil",IF(AND(C27&lt;&gt;"",OR(NOT(ISNUMBER(C27)),C27&lt;0)),"FEIL: trykkfall",IF(AND(C27="",H27&lt;&gt;"",OR(NOT(ISNUMBER(H27)),H27&lt;=0,G27="",NOT(ISNUMBER(I27)),I27&lt;=0,I27&gt;100,E27="",M27&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C27="",H27="",OR(NOT(ISNUMBER(Q27)),Q27&lt;=0)),"FEIL: lokal ID",IF(AND(C27="",H27="",ABS(Q27-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q27)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C27="",H27="",N27&lt;&gt;"",OR(NOT(ISNUMBER(N27)),N27&lt;0,E27="",NOT(ISNUMBER(I27)),I27&lt;=0,I27&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C27="",H27="",N27="",OR(Z27&lt;=0,AND(AB27&lt;&gt;"",G27&lt;&gt;AB27))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C27="",H27="",N27="",I27&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C27="",H27="",N27="",AA27&gt;0,AA27&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G27" s="16"/>
+      <c r="G27" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H27" s="16"/>
       <c r="I27" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J27" s="14" t="str">
-        <f aca="false">IFERROR(IF(C27&lt;&gt;"",C27,IF(AND(H27&gt;0,ISNUMBER(H27)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H27)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C27&lt;&gt;"",C27,IF(H27&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H27)^2,IF(ISNUMBER(O27),O27*Beregning!$B$25*(Trykkberegning!$E$12/Q27)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K27" s="27" t="str">
@@ -12617,14 +14881,68 @@
         <v/>
       </c>
       <c r="L27" s="27" t="str">
-        <f aca="false">IF(C27&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C27&lt;&gt;"","Eget trykkfall",IF(H27&lt;&gt;"","Dokumentert Kv",IF(N27&lt;&gt;"","Eget K",IF(Z27&lt;=0,"Ingen generell modell",IF(A27="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M27" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N27" s="42"/>
+      <c r="O27" s="35" t="str">
+        <f aca="false">IFERROR(IF(C27&lt;&gt;"","",IF(H27&lt;&gt;"",200*(3600*PI()*(Q27/1000)^2/4/H27)^2,IF(N27&lt;&gt;"",N27,IF(Z27&gt;0,Z27*Y27,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="14" t="n">
+        <f aca="false">IF(P27="",Trykkberegning!$E$12,P27)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R27" s="14" t="str">
+        <f aca="false">IFERROR(IF(O27&gt;0,3600*PI()*(Q27/1000)^2/4*SQRT(200/O27),""),"")</f>
+        <v/>
+      </c>
+      <c r="S27" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q27/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q27/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T27" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q27/1000)^(-1.0112))/3.7+2.51/((7500000*(Q27/1000))*SQRT(S27))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U27" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q27/1000)^(-1.0112))/3.7+2.51/((7500000*(Q27/1000))*SQRT(T27))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V27" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q27/1000)^(-1.0112))/3.7+2.51/((7500000*(Q27/1000))*SQRT(U27))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W27" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q27/1000)^(-1.0112))/3.7+2.51/((7500000*(Q27/1000))*SQRT(V27))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X27" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q27/1000)^(-1.0112))/3.7+2.51/((7500000*(Q27/1000))*SQRT(W27))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y27" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q27/1000)^(-1.0112))/3.7+2.51/((7500000*(Q27/1000))*SQRT(X27))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z27" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A27&amp;"|"&amp;G27,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA27" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q27,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB27" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q27-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
       <c r="B28" s="18" t="n">
         <v>0</v>
@@ -12636,16 +14954,19 @@
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B28="",B28=0),"Ikke med",IF(OR(NOT(ISNUMBER(B28)),B28&lt;0,B28&lt;&gt;INT(B28)),"FEIL: antall",IF(A28="","FEIL: angi ventil",IF(AND(C28&lt;&gt;"",OR(NOT(ISNUMBER(C28)),C28&lt;0)),"FEIL: trykkfall",IF(AND(C28="",OR(NOT(ISNUMBER(H28)),H28&lt;=0,G28="",NOT(ISNUMBER(I28)),I28&lt;=0,I28&gt;100,E28="",M28&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B28="",B28=0),"Ikke med",IF(OR(NOT(ISNUMBER(B28)),B28&lt;0,B28&lt;&gt;INT(B28)),"FEIL: antall",IF(A28="","FEIL: angi ventil",IF(AND(C28&lt;&gt;"",OR(NOT(ISNUMBER(C28)),C28&lt;0)),"FEIL: trykkfall",IF(AND(C28="",H28&lt;&gt;"",OR(NOT(ISNUMBER(H28)),H28&lt;=0,G28="",NOT(ISNUMBER(I28)),I28&lt;=0,I28&gt;100,E28="",M28&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C28="",H28="",OR(NOT(ISNUMBER(Q28)),Q28&lt;=0)),"FEIL: lokal ID",IF(AND(C28="",H28="",ABS(Q28-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q28)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C28="",H28="",N28&lt;&gt;"",OR(NOT(ISNUMBER(N28)),N28&lt;0,E28="",NOT(ISNUMBER(I28)),I28&lt;=0,I28&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C28="",H28="",N28="",OR(Z28&lt;=0,AND(AB28&lt;&gt;"",G28&lt;&gt;AB28))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C28="",H28="",N28="",I28&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C28="",H28="",N28="",AA28&gt;0,AA28&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G28" s="16"/>
+      <c r="G28" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H28" s="16"/>
       <c r="I28" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J28" s="14" t="str">
-        <f aca="false">IFERROR(IF(C28&lt;&gt;"",C28,IF(AND(H28&gt;0,ISNUMBER(H28)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H28)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C28&lt;&gt;"",C28,IF(H28&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H28)^2,IF(ISNUMBER(O28),O28*Beregning!$B$25*(Trykkberegning!$E$12/Q28)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K28" s="27" t="str">
@@ -12653,14 +14974,68 @@
         <v/>
       </c>
       <c r="L28" s="27" t="str">
-        <f aca="false">IF(C28&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C28&lt;&gt;"","Eget trykkfall",IF(H28&lt;&gt;"","Dokumentert Kv",IF(N28&lt;&gt;"","Eget K",IF(Z28&lt;=0,"Ingen generell modell",IF(A28="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M28" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N28" s="42"/>
+      <c r="O28" s="35" t="str">
+        <f aca="false">IFERROR(IF(C28&lt;&gt;"","",IF(H28&lt;&gt;"",200*(3600*PI()*(Q28/1000)^2/4/H28)^2,IF(N28&lt;&gt;"",N28,IF(Z28&gt;0,Z28*Y28,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="14" t="n">
+        <f aca="false">IF(P28="",Trykkberegning!$E$12,P28)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R28" s="14" t="str">
+        <f aca="false">IFERROR(IF(O28&gt;0,3600*PI()*(Q28/1000)^2/4*SQRT(200/O28),""),"")</f>
+        <v/>
+      </c>
+      <c r="S28" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q28/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q28/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T28" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q28/1000)^(-1.0112))/3.7+2.51/((7500000*(Q28/1000))*SQRT(S28))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U28" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q28/1000)^(-1.0112))/3.7+2.51/((7500000*(Q28/1000))*SQRT(T28))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V28" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q28/1000)^(-1.0112))/3.7+2.51/((7500000*(Q28/1000))*SQRT(U28))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W28" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q28/1000)^(-1.0112))/3.7+2.51/((7500000*(Q28/1000))*SQRT(V28))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X28" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q28/1000)^(-1.0112))/3.7+2.51/((7500000*(Q28/1000))*SQRT(W28))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y28" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q28/1000)^(-1.0112))/3.7+2.51/((7500000*(Q28/1000))*SQRT(X28))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z28" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A28&amp;"|"&amp;G28,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA28" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q28,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB28" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q28-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6"/>
       <c r="B29" s="18" t="n">
         <v>0</v>
@@ -12672,16 +15047,19 @@
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B29="",B29=0),"Ikke med",IF(OR(NOT(ISNUMBER(B29)),B29&lt;0,B29&lt;&gt;INT(B29)),"FEIL: antall",IF(A29="","FEIL: angi ventil",IF(AND(C29&lt;&gt;"",OR(NOT(ISNUMBER(C29)),C29&lt;0)),"FEIL: trykkfall",IF(AND(C29="",OR(NOT(ISNUMBER(H29)),H29&lt;=0,G29="",NOT(ISNUMBER(I29)),I29&lt;=0,I29&gt;100,E29="",M29&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B29="",B29=0),"Ikke med",IF(OR(NOT(ISNUMBER(B29)),B29&lt;0,B29&lt;&gt;INT(B29)),"FEIL: antall",IF(A29="","FEIL: angi ventil",IF(AND(C29&lt;&gt;"",OR(NOT(ISNUMBER(C29)),C29&lt;0)),"FEIL: trykkfall",IF(AND(C29="",H29&lt;&gt;"",OR(NOT(ISNUMBER(H29)),H29&lt;=0,G29="",NOT(ISNUMBER(I29)),I29&lt;=0,I29&gt;100,E29="",M29&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C29="",H29="",OR(NOT(ISNUMBER(Q29)),Q29&lt;=0)),"FEIL: lokal ID",IF(AND(C29="",H29="",ABS(Q29-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q29)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C29="",H29="",N29&lt;&gt;"",OR(NOT(ISNUMBER(N29)),N29&lt;0,E29="",NOT(ISNUMBER(I29)),I29&lt;=0,I29&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C29="",H29="",N29="",OR(Z29&lt;=0,AND(AB29&lt;&gt;"",G29&lt;&gt;AB29))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C29="",H29="",N29="",I29&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C29="",H29="",N29="",AA29&gt;0,AA29&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G29" s="16"/>
+      <c r="G29" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H29" s="16"/>
       <c r="I29" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J29" s="14" t="str">
-        <f aca="false">IFERROR(IF(C29&lt;&gt;"",C29,IF(AND(H29&gt;0,ISNUMBER(H29)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H29)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C29&lt;&gt;"",C29,IF(H29&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H29)^2,IF(ISNUMBER(O29),O29*Beregning!$B$25*(Trykkberegning!$E$12/Q29)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K29" s="27" t="str">
@@ -12689,14 +15067,68 @@
         <v/>
       </c>
       <c r="L29" s="27" t="str">
-        <f aca="false">IF(C29&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C29&lt;&gt;"","Eget trykkfall",IF(H29&lt;&gt;"","Dokumentert Kv",IF(N29&lt;&gt;"","Eget K",IF(Z29&lt;=0,"Ingen generell modell",IF(A29="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M29" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N29" s="42"/>
+      <c r="O29" s="35" t="str">
+        <f aca="false">IFERROR(IF(C29&lt;&gt;"","",IF(H29&lt;&gt;"",200*(3600*PI()*(Q29/1000)^2/4/H29)^2,IF(N29&lt;&gt;"",N29,IF(Z29&gt;0,Z29*Y29,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="14" t="n">
+        <f aca="false">IF(P29="",Trykkberegning!$E$12,P29)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R29" s="14" t="str">
+        <f aca="false">IFERROR(IF(O29&gt;0,3600*PI()*(Q29/1000)^2/4*SQRT(200/O29),""),"")</f>
+        <v/>
+      </c>
+      <c r="S29" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q29/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q29/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T29" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q29/1000)^(-1.0112))/3.7+2.51/((7500000*(Q29/1000))*SQRT(S29))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U29" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q29/1000)^(-1.0112))/3.7+2.51/((7500000*(Q29/1000))*SQRT(T29))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V29" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q29/1000)^(-1.0112))/3.7+2.51/((7500000*(Q29/1000))*SQRT(U29))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W29" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q29/1000)^(-1.0112))/3.7+2.51/((7500000*(Q29/1000))*SQRT(V29))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X29" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q29/1000)^(-1.0112))/3.7+2.51/((7500000*(Q29/1000))*SQRT(W29))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y29" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q29/1000)^(-1.0112))/3.7+2.51/((7500000*(Q29/1000))*SQRT(X29))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z29" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A29&amp;"|"&amp;G29,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA29" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q29,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB29" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q29-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
       <c r="B30" s="18" t="n">
         <v>0</v>
@@ -12708,16 +15140,19 @@
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B30="",B30=0),"Ikke med",IF(OR(NOT(ISNUMBER(B30)),B30&lt;0,B30&lt;&gt;INT(B30)),"FEIL: antall",IF(A30="","FEIL: angi ventil",IF(AND(C30&lt;&gt;"",OR(NOT(ISNUMBER(C30)),C30&lt;0)),"FEIL: trykkfall",IF(AND(C30="",OR(NOT(ISNUMBER(H30)),H30&lt;=0,G30="",NOT(ISNUMBER(I30)),I30&lt;=0,I30&gt;100,E30="",M30&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B30="",B30=0),"Ikke med",IF(OR(NOT(ISNUMBER(B30)),B30&lt;0,B30&lt;&gt;INT(B30)),"FEIL: antall",IF(A30="","FEIL: angi ventil",IF(AND(C30&lt;&gt;"",OR(NOT(ISNUMBER(C30)),C30&lt;0)),"FEIL: trykkfall",IF(AND(C30="",H30&lt;&gt;"",OR(NOT(ISNUMBER(H30)),H30&lt;=0,G30="",NOT(ISNUMBER(I30)),I30&lt;=0,I30&gt;100,E30="",M30&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C30="",H30="",OR(NOT(ISNUMBER(Q30)),Q30&lt;=0)),"FEIL: lokal ID",IF(AND(C30="",H30="",ABS(Q30-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q30)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C30="",H30="",N30&lt;&gt;"",OR(NOT(ISNUMBER(N30)),N30&lt;0,E30="",NOT(ISNUMBER(I30)),I30&lt;=0,I30&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C30="",H30="",N30="",OR(Z30&lt;=0,AND(AB30&lt;&gt;"",G30&lt;&gt;AB30))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C30="",H30="",N30="",I30&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C30="",H30="",N30="",AA30&gt;0,AA30&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G30" s="16"/>
+      <c r="G30" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H30" s="16"/>
       <c r="I30" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J30" s="14" t="str">
-        <f aca="false">IFERROR(IF(C30&lt;&gt;"",C30,IF(AND(H30&gt;0,ISNUMBER(H30)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H30)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C30&lt;&gt;"",C30,IF(H30&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H30)^2,IF(ISNUMBER(O30),O30*Beregning!$B$25*(Trykkberegning!$E$12/Q30)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K30" s="27" t="str">
@@ -12725,14 +15160,68 @@
         <v/>
       </c>
       <c r="L30" s="27" t="str">
-        <f aca="false">IF(C30&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C30&lt;&gt;"","Eget trykkfall",IF(H30&lt;&gt;"","Dokumentert Kv",IF(N30&lt;&gt;"","Eget K",IF(Z30&lt;=0,"Ingen generell modell",IF(A30="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M30" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N30" s="42"/>
+      <c r="O30" s="35" t="str">
+        <f aca="false">IFERROR(IF(C30&lt;&gt;"","",IF(H30&lt;&gt;"",200*(3600*PI()*(Q30/1000)^2/4/H30)^2,IF(N30&lt;&gt;"",N30,IF(Z30&gt;0,Z30*Y30,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P30" s="16"/>
+      <c r="Q30" s="14" t="n">
+        <f aca="false">IF(P30="",Trykkberegning!$E$12,P30)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R30" s="14" t="str">
+        <f aca="false">IFERROR(IF(O30&gt;0,3600*PI()*(Q30/1000)^2/4*SQRT(200/O30),""),"")</f>
+        <v/>
+      </c>
+      <c r="S30" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q30/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q30/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T30" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q30/1000)^(-1.0112))/3.7+2.51/((7500000*(Q30/1000))*SQRT(S30))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U30" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q30/1000)^(-1.0112))/3.7+2.51/((7500000*(Q30/1000))*SQRT(T30))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V30" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q30/1000)^(-1.0112))/3.7+2.51/((7500000*(Q30/1000))*SQRT(U30))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W30" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q30/1000)^(-1.0112))/3.7+2.51/((7500000*(Q30/1000))*SQRT(V30))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X30" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q30/1000)^(-1.0112))/3.7+2.51/((7500000*(Q30/1000))*SQRT(W30))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y30" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q30/1000)^(-1.0112))/3.7+2.51/((7500000*(Q30/1000))*SQRT(X30))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z30" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A30&amp;"|"&amp;G30,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA30" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q30,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB30" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q30-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6"/>
       <c r="B31" s="18" t="n">
         <v>0</v>
@@ -12744,16 +15233,19 @@
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="27" t="str">
-        <f aca="false">IFERROR(IF(OR(B31="",B31=0),"Ikke med",IF(OR(NOT(ISNUMBER(B31)),B31&lt;0,B31&lt;&gt;INT(B31)),"FEIL: antall",IF(A31="","FEIL: angi ventil",IF(AND(C31&lt;&gt;"",OR(NOT(ISNUMBER(C31)),C31&lt;0)),"FEIL: trykkfall",IF(AND(C31="",OR(NOT(ISNUMBER(H31)),H31&lt;=0,G31="",NOT(ISNUMBER(I31)),I31&lt;=0,I31&gt;100,E31="",M31&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium","OK"))))),"FEIL: kontroller tall")</f>
+        <f aca="false">IFERROR(IF(OR(B31="",B31=0),"Ikke med",IF(OR(NOT(ISNUMBER(B31)),B31&lt;0,B31&lt;&gt;INT(B31)),"FEIL: antall",IF(A31="","FEIL: angi ventil",IF(AND(C31&lt;&gt;"",OR(NOT(ISNUMBER(C31)),C31&lt;0)),"FEIL: trykkfall",IF(AND(C31="",H31&lt;&gt;"",OR(NOT(ISNUMBER(H31)),H31&lt;=0,G31="",NOT(ISNUMBER(I31)),I31&lt;=0,I31&gt;100,E31="",M31&lt;&gt;"Ja")),"FEIL: dokumenter Kv, DN, åpning og medium",IF(AND(C31="",H31="",OR(NOT(ISNUMBER(Q31)),Q31&lt;=0)),"FEIL: lokal ID",IF(AND(C31="",H31="",ABS(Q31-Trykkberegning!$E$12)&gt;0.000001,COUNTIFS(Reduksjoner!$B$7:$B$31,1,Reduksjoner!$D$7:$D$31,Q31)=0),"FEIL: lokal ID mangler i reduksjonskjeden",IF(AND(C31="",H31="",N31&lt;&gt;"",OR(NOT(ISNUMBER(N31)),N31&lt;0,E31="",NOT(ISNUMBER(I31)),I31&lt;=0,I31&gt;100)),"FEIL: dokumenter eget K og åpning",IF(AND(C31="",H31="",N31="",OR(Z31&lt;=0,AND(AB31&lt;&gt;"",G31&lt;&gt;AB31))),"FEIL: ingen generell modell for DN / lokal ID",IF(AND(C31="",H31="",N31="",I31&lt;&gt;100),"FEIL: generell modell krever 100 % åpning",IF(AND(C31="",H31="",N31="",AA31&gt;0,AA31&lt;4000),"FEIL: generell modell krever Re &gt;=4000","OK"))))))))))),"FEIL: kontroller ventilinndata")</f>
         <v>Ikke med</v>
       </c>
-      <c r="G31" s="16"/>
+      <c r="G31" s="16" t="str">
+        <f aca="false">Trykkberegning!E7</f>
+        <v>DN80</v>
+      </c>
       <c r="H31" s="16"/>
       <c r="I31" s="16" t="n">
         <v>100</v>
       </c>
       <c r="J31" s="14" t="str">
-        <f aca="false">IFERROR(IF(C31&lt;&gt;"",C31,IF(AND(H31&gt;0,ISNUMBER(H31)),100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H31)^2,"")),"")</f>
+        <f aca="false">IFERROR(IF(C31&lt;&gt;"",C31,IF(H31&lt;&gt;"",100*(Beregning!$B$10/1000)*(Trykkberegning!$E$25/H31)^2,IF(ISNUMBER(O31),O31*Beregning!$B$25*(Trykkberegning!$E$12/Q31)^4/1000,""))),"")</f>
         <v/>
       </c>
       <c r="K31" s="27" t="str">
@@ -12761,17 +15253,71 @@
         <v/>
       </c>
       <c r="L31" s="27" t="str">
-        <f aca="false">IF(C31&lt;&gt;"","Eget trykkfall","Kv ved angitt åpning")</f>
-        <v>Kv ved angitt åpning</v>
+        <f aca="false">IF(C31&lt;&gt;"","Eget trykkfall",IF(H31&lt;&gt;"","Dokumentert Kv",IF(N31&lt;&gt;"","Eget K",IF(Z31&lt;=0,"Ingen generell modell",IF(A31="Generelt skyvespjeld – sluseanslag","ANSLAG: skyvespjeld fra sluse","Modellestimat: Crane, full åpning")))))</f>
+        <v>Ingen generell modell</v>
       </c>
       <c r="M31" s="16" t="s">
         <v>90</v>
+      </c>
+      <c r="N31" s="42"/>
+      <c r="O31" s="35" t="str">
+        <f aca="false">IFERROR(IF(C31&lt;&gt;"","",IF(H31&lt;&gt;"",200*(3600*PI()*(Q31/1000)^2/4/H31)^2,IF(N31&lt;&gt;"",N31,IF(Z31&gt;0,Z31*Y31,"")))),"")</f>
+        <v/>
+      </c>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="14" t="n">
+        <f aca="false">IF(P31="",Trykkberegning!$E$12,P31)</f>
+        <v>82.5</v>
+      </c>
+      <c r="R31" s="14" t="str">
+        <f aca="false">IFERROR(IF(O31&gt;0,3600*PI()*(Q31/1000)^2/4*SQRT(200/O31),""),"")</f>
+        <v/>
+      </c>
+      <c r="S31" s="27" t="n">
+        <f aca="false">IFERROR((-1.8*LOG10(((0.000034126825352925*(Q31/1000)^(-1.0112))/3.7)^1.11+6.9/(7500000*(Q31/1000))))^(-2),"")</f>
+        <v>0.0169172221919985</v>
+      </c>
+      <c r="T31" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q31/1000)^(-1.0112))/3.7+2.51/((7500000*(Q31/1000))*SQRT(S31))))^(-2),"")</f>
+        <v>0.0169968277066495</v>
+      </c>
+      <c r="U31" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q31/1000)^(-1.0112))/3.7+2.51/((7500000*(Q31/1000))*SQRT(T31))))^(-2),"")</f>
+        <v>0.0169949015157495</v>
+      </c>
+      <c r="V31" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q31/1000)^(-1.0112))/3.7+2.51/((7500000*(Q31/1000))*SQRT(U31))))^(-2),"")</f>
+        <v>0.0169949479708735</v>
+      </c>
+      <c r="W31" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q31/1000)^(-1.0112))/3.7+2.51/((7500000*(Q31/1000))*SQRT(V31))))^(-2),"")</f>
+        <v>0.0169949468503983</v>
+      </c>
+      <c r="X31" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q31/1000)^(-1.0112))/3.7+2.51/((7500000*(Q31/1000))*SQRT(W31))))^(-2),"")</f>
+        <v>0.0169949468774235</v>
+      </c>
+      <c r="Y31" s="27" t="n">
+        <f aca="false">IFERROR((-2*LOG10((0.000034126825352925*(Q31/1000)^(-1.0112))/3.7+2.51/((7500000*(Q31/1000))*SQRT(X31))))^(-2),"")</f>
+        <v>0.0169949468767717</v>
+      </c>
+      <c r="Z31" s="27" t="n">
+        <f aca="false">IFERROR(VLOOKUP(A31&amp;"|"&amp;G31,GenerelleVentildata,5,FALSE()),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA31" s="27" t="n">
+        <f aca="false">IFERROR(Beregning!$B$14*Trykkberegning!$E$12/Q31,"")</f>
+        <v>153746.774760133</v>
+      </c>
+      <c r="AB31" s="27" t="str">
+        <f aca="false">IFERROR(IF(AND(ABS(Q31-Trykkberegning!$E$12)&lt;0.000001,Trykkberegning!$E$6&lt;&gt;"Metrisk OD"),Trykkberegning!$E$7,""),"")</f>
+        <v>DN80</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="24" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B33" s="24"/>
       <c r="C33" s="24"/>
@@ -12783,7 +15329,7 @@
     <row r="34" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B35" s="26"/>
       <c r="C35" s="26"/>
@@ -12818,12 +15364,12 @@
     <row r="53" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="54" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A6:F31"/>
+  <autoFilter ref="A6:R31"/>
   <mergeCells count="6">
     <mergeCell ref="A1:M2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A4:R4"/>
+    <mergeCell ref="A5:R5"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A35:F36"/>
   </mergeCells>
@@ -12832,7 +15378,7 @@
       <formula>LEFT(F7,4)="FEIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7">
+  <dataValidations xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9">
     <dataValidation sqref="B7:B31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig tall" error="Oppgi et heltall mellom 0 og 100000." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100000</formula2>
@@ -12858,6 +15404,14 @@
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
+    <dataValidation sqref="N7:N31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig tall" error="Oppgi et tall mellom 0 og 1000000000.0." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
+    <dataValidation sqref="P7:P31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig tall" error="Oppgi et tall mellom 1e-09 og 1000000000.0." type="decimal" operator="between">
+      <formula1>1e-09</formula1>
+      <formula2>1000000000.0</formula2>
+    </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.15"/>
@@ -12866,11 +15420,1480 @@
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 R-rdimensjonering | &amp;A | side &amp;P av &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF087F8C"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:J54"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="90"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="85"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+    </row>
+    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="35" t="n">
+        <v>0.0259112557442981</v>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>0.0777337672328941</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>32.268965320008</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="35" t="n">
+        <v>0.0239742097246079</v>
+      </c>
+      <c r="G8" s="35" t="n">
+        <v>0.0719226291738236</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>59.6395824008357</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="35" t="n">
+        <v>0.0226174412858792</v>
+      </c>
+      <c r="G9" s="35" t="n">
+        <v>0.0678523238576376</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>95.941175255472</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="35" t="n">
+        <v>0.0212464082806993</v>
+      </c>
+      <c r="G10" s="35" t="n">
+        <v>0.063739224842098</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>162.182484004164</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="35" t="n">
+        <v>0.0201115704540326</v>
+      </c>
+      <c r="G11" s="35" t="n">
+        <v>0.0603347113620977</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>260.461623287242</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="35" t="n">
+        <v>0.0190652576049004</v>
+      </c>
+      <c r="G12" s="35" t="n">
+        <v>0.0571957728147013</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>417.989548207481</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="35" t="n">
+        <v>0.0179361899403161</v>
+      </c>
+      <c r="G13" s="35" t="n">
+        <v>0.0538085698209483</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>728.296744597051</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="35" t="n">
+        <v>0.0171122136960254</v>
+      </c>
+      <c r="G14" s="35" t="n">
+        <v>0.0513366410880761</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>1129.46721469292</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="35" t="n">
+        <v>0.0162884254312255</v>
+      </c>
+      <c r="G15" s="35" t="n">
+        <v>0.0488652762936764</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>1808.86935250739</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="35" t="n">
+        <v>0.0155227021855393</v>
+      </c>
+      <c r="G16" s="35" t="n">
+        <v>0.0465681065566179</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>2895.23030493845</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="35" t="n">
+        <v>0.0149364280452892</v>
+      </c>
+      <c r="G17" s="35" t="n">
+        <v>0.0448092841358677</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>4250.16602390575</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="35" t="n">
+        <v>0.0140766911224689</v>
+      </c>
+      <c r="G18" s="35" t="n">
+        <v>0.0422300733674068</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>7783.16886938451</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="35" t="n">
+        <v>0.013459915829792</v>
+      </c>
+      <c r="G19" s="35" t="n">
+        <v>0.0403797474893758</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>12436.7125878833</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="35" t="n">
+        <v>0.0129855626731891</v>
+      </c>
+      <c r="G20" s="35" t="n">
+        <v>0.0389566880195674</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>18233.0312249449</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E21" s="14"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="E24" s="14"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E25" s="14"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F26" s="35" t="n">
+        <v>0.0190652576049004</v>
+      </c>
+      <c r="G26" s="35" t="n">
+        <v>0.152522060839203</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>255.9652777312</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="35" t="n">
+        <v>0.0179361899403161</v>
+      </c>
+      <c r="G27" s="35" t="n">
+        <v>0.143489519522529</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>445.988851398214</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="35" t="n">
+        <v>0.0171122136960254</v>
+      </c>
+      <c r="G28" s="35" t="n">
+        <v>0.136897709568203</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>691.654589300045</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" s="35" t="n">
+        <v>0.0162884254312255</v>
+      </c>
+      <c r="G29" s="35" t="n">
+        <v>0.130307403449804</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>1107.70173125043</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="35" t="n">
+        <v>0.0155227021855393</v>
+      </c>
+      <c r="G30" s="35" t="n">
+        <v>0.124181617484314</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>1772.95923373544</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" s="35" t="n">
+        <v>0.0149364280452892</v>
+      </c>
+      <c r="G31" s="35" t="n">
+        <v>0.119491424362314</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>2602.68452017067</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="35" t="n">
+        <v>0.0140766911224689</v>
+      </c>
+      <c r="G32" s="35" t="n">
+        <v>0.112613528979751</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>4766.19807797668</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="35" t="n">
+        <v>0.013459915829792</v>
+      </c>
+      <c r="G33" s="35" t="n">
+        <v>0.107679326638336</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>7615.89997949064</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" s="35" t="n">
+        <v>0.0129855626731891</v>
+      </c>
+      <c r="G34" s="35" t="n">
+        <v>0.103884501385513</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>11165.405741337</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E35" s="14"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" s="14"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E37" s="14"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="E38" s="14"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" s="14"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="F40" s="35" t="n">
+        <v>0.0190652576049004</v>
+      </c>
+      <c r="G40" s="35" t="n">
+        <v>0.857936592220519</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>107.924437273089</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="F41" s="35" t="n">
+        <v>0.0179361899403161</v>
+      </c>
+      <c r="G41" s="35" t="n">
+        <v>0.807128547314224</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>188.04541086143</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="F42" s="35" t="n">
+        <v>0.0171122136960254</v>
+      </c>
+      <c r="G42" s="35" t="n">
+        <v>0.770049616321141</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>291.627180839529</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="F43" s="35" t="n">
+        <v>0.0162884254312255</v>
+      </c>
+      <c r="G43" s="35" t="n">
+        <v>0.732979144405147</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>467.048058515075</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="F44" s="35" t="n">
+        <v>0.0155227021855393</v>
+      </c>
+      <c r="G44" s="35" t="n">
+        <v>0.698521598349268</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>747.545250297444</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="J44" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="F45" s="35" t="n">
+        <v>0.0149364280452892</v>
+      </c>
+      <c r="G45" s="35" t="n">
+        <v>0.672139262038016</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>1097.38814861357</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="J45" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="F46" s="35" t="n">
+        <v>0.0140766911224689</v>
+      </c>
+      <c r="G46" s="35" t="n">
+        <v>0.633451100511101</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>2009.60556078975</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="J46" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="F47" s="35" t="n">
+        <v>0.013459915829792</v>
+      </c>
+      <c r="G47" s="35" t="n">
+        <v>0.471097054042718</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>3641.09661652657</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="F48" s="35" t="n">
+        <v>0.0129855626731891</v>
+      </c>
+      <c r="G48" s="35" t="n">
+        <v>0.45449469356162</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>5338.08495074897</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="36"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="36"/>
+    </row>
+    <row r="51" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="36"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="36"/>
+      <c r="D51" s="36"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="36"/>
+      <c r="H51" s="36"/>
+      <c r="I51" s="36"/>
+      <c r="J51" s="36"/>
+    </row>
+    <row r="52" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="36"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="36"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="36"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="36"/>
+      <c r="J52" s="36"/>
+    </row>
+    <row r="53" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+    </row>
+    <row r="54" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:J48"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J5"/>
+    <mergeCell ref="A50:J52"/>
+    <mergeCell ref="A53:J54"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.15"/>
+  <pageSetup paperSize="8" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 R-rdimensjonering | &amp;A | side &amp;P av &amp;N</oddFooter>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF087F8C"/>
@@ -12888,7 +16911,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12916,7 +16939,7 @@
     </row>
     <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
-        <v>181</v>
+        <v>259</v>
       </c>
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
@@ -12926,7 +16949,7 @@
     </row>
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="s">
-        <v>182</v>
+        <v>260</v>
       </c>
       <c r="B5" s="37"/>
       <c r="C5" s="37"/>
@@ -12956,7 +16979,7 @@
     </row>
     <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>183</v>
+        <v>261</v>
       </c>
       <c r="B7" s="18" t="n">
         <v>0</v>
@@ -12974,7 +16997,7 @@
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>184</v>
+        <v>262</v>
       </c>
       <c r="B8" s="18" t="n">
         <v>0</v>
@@ -12992,7 +17015,7 @@
     </row>
     <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>185</v>
+        <v>263</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>0</v>
@@ -13010,7 +17033,7 @@
     </row>
     <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>186</v>
+        <v>264</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>0</v>
@@ -13028,7 +17051,7 @@
     </row>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>187</v>
+        <v>265</v>
       </c>
       <c r="B11" s="18" t="n">
         <v>0</v>
@@ -13367,7 +17390,7 @@
     <row r="32" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="24" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B33" s="24"/>
       <c r="C33" s="24"/>
@@ -13379,7 +17402,7 @@
     <row r="34" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B35" s="26"/>
       <c r="C35" s="26"/>
@@ -13449,7 +17472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF087F8C"/>
@@ -13458,15 +17481,16 @@
   <dimension ref="A1:E54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>266</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13482,7 +17506,7 @@
     </row>
     <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>189</v>
+        <v>267</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -13491,7 +17515,7 @@
     </row>
     <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="28" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
@@ -13507,27 +17531,27 @@
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>191</v>
+        <v>269</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>192</v>
+        <v>270</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>193</v>
+        <v>271</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>194</v>
+        <v>272</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>195</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>197</v>
+        <v>275</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
@@ -13535,10 +17559,10 @@
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>173</v>
+        <v>276</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>198</v>
+        <v>277</v>
       </c>
       <c r="C8" s="27"/>
       <c r="D8" s="27"/>
@@ -13546,10 +17570,10 @@
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>198</v>
+        <v>277</v>
       </c>
       <c r="C9" s="27"/>
       <c r="D9" s="27"/>
@@ -13557,10 +17581,10 @@
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>175</v>
+        <v>279</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>198</v>
+        <v>277</v>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
@@ -13568,10 +17592,10 @@
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>198</v>
+        <v>277</v>
       </c>
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
@@ -13579,18 +17603,66 @@
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>198</v>
+        <v>277</v>
       </c>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
       <c r="E12" s="27"/>
     </row>
-    <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>281</v>
+      </c>
+    </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -13631,7 +17703,7 @@
     <row r="53" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="54" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A6:E12"/>
+  <autoFilter ref="A6:E15"/>
   <mergeCells count="3">
     <mergeCell ref="A1:E2"/>
     <mergeCell ref="A3:E3"/>
@@ -13646,260 +17718,4 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:C54"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="115"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>207</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>211</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>213</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="n">
-        <v>14</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>229</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C23" s="42" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="48" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="A3:C3"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C23" r:id="rId1" display="Dokumentert referanseimplementasjon: fluids / fittings.py"/>
-  </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.15"/>
-  <pageSetup paperSize="8" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 R-rdimensjonering | &amp;A | side &amp;P av &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>
--- a/workbooks/Trykkberegning_ror.xlsx
+++ b/workbooks/Trykkberegning_ror.xlsx
@@ -1329,7 +1329,7 @@
     <t xml:space="preserve">TRYKKBEREGNING AV RØR</t>
   </si>
   <si>
-    <t xml:space="preserve">Væsker · én rørstrekning · eksempeldata ved åpning · blå felt er inndata</t>
+    <t xml:space="preserve">Væsker · én rørstrekning · eksempeldata ved åpning · lysegrønne felt er inndata</t>
   </si>
   <si>
     <t xml:space="preserve">1  RØR OG MATERIALE</t>
@@ -2187,7 +2187,7 @@
     <t xml:space="preserve">1. Rør og materiale</t>
   </si>
   <si>
-    <t xml:space="preserve">Velg rørserie, DN/OD, materiale og EN-produktstandard. Oppgi faktisk veggtykkelse. Ved kjent lysåpning kan du overstyre ID. Metrisk OD er ikke en automatisk material- eller veggserie. En svart/grå verdi er beregnet; blå felt er inndata.</t>
+    <t xml:space="preserve">Velg rørserie, DN/OD, materiale og EN-produktstandard. Oppgi faktisk veggtykkelse. Ved kjent lysåpning kan du overstyre ID. Metrisk OD er ikke en automatisk material- eller veggserie. En mørk verdi er beregnet; lysegrønne felt er inndata.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Væske og drift</t>
@@ -2830,7 +2830,7 @@
     <numFmt numFmtId="181" formatCode="0.0000"/>
     <numFmt numFmtId="182" formatCode="0.0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2863,7 +2863,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF617589"/>
+      <color rgb="FF005149"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2878,21 +2878,14 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF20354C"/>
+      <color rgb="FF1A1C1B"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF086AA5"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF617589"/>
+      <color rgb="FF005149"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2907,7 +2900,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF20354C"/>
+      <color rgb="FF1A1C1B"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2915,7 +2908,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF20354C"/>
+      <color rgb="FF1A1C1B"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2931,7 +2924,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF086AA5"/>
+      <color rgb="FF005149"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2944,20 +2937,20 @@
     <font>
       <b val="true"/>
       <sz val="18"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF1A1C1B"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF1A1C1B"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF1A1C1B"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2972,7 +2965,7 @@
     <font>
       <u val="single"/>
       <sz val="11"/>
-      <color rgb="FF086AA5"/>
+      <color rgb="FF005149"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2986,7 +2979,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2995,38 +2988,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF142D4E"/>
-        <bgColor rgb="FF20354C"/>
+        <fgColor rgb="FF022B2A"/>
+        <bgColor rgb="FF1A1C1B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF087F8C"/>
-        <bgColor rgb="FF008080"/>
+        <fgColor rgb="FF005149"/>
+        <bgColor rgb="FF022B2A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE5F2FF"/>
-        <bgColor rgb="FFE1F3EB"/>
+        <fgColor rgb="FFC0FFDE"/>
+        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
-        <bgColor rgb="FFF9F9F9"/>
+        <fgColor rgb="FFF5FAF6"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3EB"/>
-        <bgColor rgb="FFE5F2FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF0CE"/>
-        <bgColor rgb="FFFFE5E5"/>
+        <fgColor rgb="FFFFF0EB"/>
+        <bgColor rgb="FFF5FAF6"/>
       </patternFill>
     </fill>
   </fills>
@@ -3043,7 +3030,7 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFD6E1EA"/>
+        <color rgb="FF40C1AC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3102,19 +3089,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3122,19 +3109,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3142,7 +3129,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3150,31 +3137,31 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3182,39 +3169,39 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="179" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3222,23 +3209,23 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="180" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="181" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3246,23 +3233,23 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="182" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3279,21 +3266,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFE5E5"/>
+          <bgColor rgb="FFFF4B1A"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFF0CE"/>
+          <bgColor rgb="FFFFF0EB"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE5F2FF"/>
+          <fgColor rgb="FFC0FFDE"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3301,7 +3288,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF1F5F9"/>
+          <fgColor rgb="FFF5FAF6"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3309,7 +3296,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF086AA5"/>
+          <fgColor rgb="FF005149"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3317,7 +3304,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF20354C"/>
+          <fgColor rgb="FF1A1C1B"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3338,16 +3325,16 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF087F8C"/>
-      <rgbColor rgb="FFF1F5F9"/>
-      <rgbColor rgb="FF878787"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF888888"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF0CE"/>
-      <rgbColor rgb="FFE1F3EB"/>
+      <rgbColor rgb="FFF5FAF6"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF086AA5"/>
+      <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -3358,29 +3345,29 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFE5F2FF"/>
-      <rgbColor rgb="FFD6E1EA"/>
-      <rgbColor rgb="FFF9F9F9"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFC0FFDE"/>
+      <rgbColor rgb="FFFFF0EB"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFE5E5"/>
-      <rgbColor rgb="FF4F81BD"/>
-      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF40C1AC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF617589"/>
+      <rgbColor rgb="FFFF4B1A"/>
+      <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF142D4E"/>
+      <rgbColor rgb="FF005149"/>
       <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF022B2A"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF20354C"/>
+      <rgbColor rgb="FF1A1C1B"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -3407,7 +3394,7 @@
             <a:r>
               <a:rPr sz="1800" b="1" u="none" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1A1C1B"/>
                 </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
@@ -3459,9 +3446,12 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="005149"/>
+            </a:solidFill>
             <a:ln w="12600">
               <a:solidFill>
-                <a:srgbClr val="F9F9F9"/>
+                <a:srgbClr val="005149"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3545,11 +3535,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="40265228"/>
-        <c:axId val="18211899"/>
+        <c:axId val="37334958"/>
+        <c:axId val="31883330"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="40265228"/>
+        <c:axId val="37334958"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3562,7 +3552,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="888888"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -3574,7 +3564,7 @@
             <a:pPr>
               <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1A1C1B"/>
                 </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
@@ -3582,14 +3572,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18211899"/>
+        <c:crossAx val="31883330"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18211899"/>
+        <c:axId val="31883330"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3599,7 +3589,7 @@
           <c:spPr>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="878787"/>
+                <a:srgbClr val="888888"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3620,7 +3610,7 @@
                 <a:r>
                   <a:rPr sz="1000" b="1" u="none" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="1A1C1B"/>
                     </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
@@ -3645,7 +3635,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="878787"/>
+              <a:srgbClr val="888888"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -3657,7 +3647,7 @@
             <a:pPr>
               <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="1A1C1B"/>
                 </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
@@ -3665,7 +3655,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40265228"/>
+        <c:crossAx val="37334958"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3942,72 +3932,645 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>390600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>698760</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>118800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 2" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10469880" y="178920"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>5562720</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>7562520</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>118800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9087120" y="178920"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2228760</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4228560</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>118800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10193400" y="178920"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2228760</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4228560</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>118800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11744280" y="178920"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3895560</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>5895360</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>118800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9675360" y="178920"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1943280</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>77400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1476000</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>112680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8568720" y="77400"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>76320</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>948240</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>118800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11424240" y="178920"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>561960</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>2561760</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>118800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15998040" y="178920"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>895320</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>2895120</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>118800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15062760" y="178920"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>428760</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2428560</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>118800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14032440" y="178920"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>2543040</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1300680</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>118800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="26578440" y="178920"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>3562200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>5562000</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>118800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24919200" y="178920"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>162000</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2161800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>118800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11439720" y="178920"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>5610240</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1618920</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>118800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14491440" y="178920"/>
+          <a:ext cx="1999800" cy="225720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="1A1C1B"/>
       </a:dk1>
       <a:lt1>
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="022B2A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="F5FAF6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="005149"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="40C1AC"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="FF4B1A"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="C0FFDE"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="022B2A"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="1A1C1B"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="005149"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="005149"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -4147,7 +4710,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:N54"/>
@@ -4965,19 +5528,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19">
-    <dataValidation sqref="E6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Blå felt kan redigeres." type="list">
+    <dataValidation sqref="E6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Lysegrønne felt kan redigeres." type="list">
       <formula1>Rorserier</formula1>
     </dataValidation>
-    <dataValidation sqref="E7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Blå felt kan redigeres." type="list">
+    <dataValidation sqref="E7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Lysegrønne felt kan redigeres." type="list">
       <formula1>INDIRECT(IF($E$6="Metrisk OD","MetriskeOD","NominelleDN"))</formula1>
     </dataValidation>
-    <dataValidation sqref="E13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Blå felt kan redigeres." type="list">
+    <dataValidation sqref="E13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Lysegrønne felt kan redigeres." type="list">
       <formula1>Materialvalg</formula1>
     </dataValidation>
-    <dataValidation sqref="E14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Blå felt kan redigeres." type="list">
+    <dataValidation sqref="E14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Lysegrønne felt kan redigeres." type="list">
       <formula1>ENStandarder</formula1>
     </dataValidation>
-    <dataValidation sqref="E20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Blå felt kan redigeres." type="list">
+    <dataValidation sqref="E20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Lysegrønne felt kan redigeres." type="list">
       <formula1>Medievalg</formula1>
     </dataValidation>
     <dataValidation sqref="E9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig tall" error="Oppgi et tall mellom 0 og 1000000000.0." type="decimal" operator="between">
@@ -5032,7 +5595,7 @@
       <formula1>-1</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation sqref="E34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Blå felt kan redigeres." type="list">
+    <dataValidation sqref="E34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Lysegrønne felt kan redigeres." type="list">
       <formula1>"Hoveddimensjon,Rørstrekk-tabell"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5060,7 +5623,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:C54"/>
@@ -5310,13 +5873,14 @@
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 R-rdimensjonering | &amp;A | side &amp;P av &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:E54"/>
@@ -6177,7 +6741,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:E54"/>
@@ -6420,13 +6984,14 @@
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 R-rdimensjonering | &amp;A | side &amp;P av &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:D54"/>
@@ -6640,13 +7205,14 @@
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 R-rdimensjonering | &amp;A | side &amp;P av &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF617589"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E40"/>
@@ -7157,6 +7723,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7501,7 +8068,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:M54"/>
@@ -8246,7 +8813,7 @@
       <formula1>-273.14</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation sqref="E17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Blå felt kan redigeres." type="list">
+    <dataValidation sqref="E17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Lysegrønne felt kan redigeres." type="list">
       <formula1>"Nei,Ja"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8257,14 +8824,15 @@
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 R-rdimensjonering | &amp;A | side &amp;P av &amp;N</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:L54"/>
@@ -9307,13 +9875,14 @@
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 R-rdimensjonering | &amp;A | side &amp;P av &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:R54"/>
@@ -10961,13 +11530,14 @@
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 R-rdimensjonering | &amp;A | side &amp;P av &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:T54"/>
@@ -12774,7 +13344,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6">
-    <dataValidation sqref="A7:A31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Blå felt kan redigeres." type="list">
+    <dataValidation sqref="A7:A31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Lysegrønne felt kan redigeres." type="list">
       <formula1>Bendtyper</formula1>
     </dataValidation>
     <dataValidation sqref="B7:B31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig tall" error="Oppgi et tall mellom 0 og 180." type="decimal" operator="between">
@@ -12813,7 +13383,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:AB54"/>
@@ -15387,13 +15957,13 @@
       <formula1>0</formula1>
       <formula2>1000000000.0</formula2>
     </dataValidation>
-    <dataValidation sqref="A7:A31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Blå felt kan redigeres." type="list">
+    <dataValidation sqref="A7:A31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Lysegrønne felt kan redigeres." type="list">
       <formula1>Ventilvalg</formula1>
     </dataValidation>
-    <dataValidation sqref="G7:G31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Blå felt kan redigeres." type="list">
+    <dataValidation sqref="G7:G31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Lysegrønne felt kan redigeres." type="list">
       <formula1>NominelleDN</formula1>
     </dataValidation>
-    <dataValidation sqref="M7:M31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Blå felt kan redigeres." type="list">
+    <dataValidation sqref="M7:M31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig valg" error="Velg fra listen, eller bruk et felt for egne verdier." promptTitle="Velg verdi" prompt="Bruk nedtrekkslisten. Lysegrønne felt kan redigeres." type="list">
       <formula1>"Nei,Ja"</formula1>
     </dataValidation>
     <dataValidation sqref="H7:H31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ugyldig tall" error="Oppgi et tall mellom 0 og 1000000000.0." type="decimal" operator="between">
@@ -15428,7 +15998,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:J54"/>
@@ -16896,7 +17466,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:F54"/>
@@ -17475,7 +18045,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF087F8C"/>
+    <tabColor rgb="FF005149"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:E54"/>

--- a/workbooks/Trykkberegning_ror.xlsx
+++ b/workbooks/Trykkberegning_ror.xlsx
@@ -2809,7 +2809,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="19">
+  <numFmts count="20">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.000&quot; bar&quot;"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
@@ -2821,16 +2821,17 @@
     <numFmt numFmtId="172" formatCode="0.000&quot; m væskesøyle&quot;"/>
     <numFmt numFmtId="173" formatCode="0.000&quot; bar(g)&quot;"/>
     <numFmt numFmtId="174" formatCode="0.000&quot; bar&quot;;\-0.000&quot; bar&quot;;&quot;&quot;"/>
-    <numFmt numFmtId="175" formatCode="0.00&quot; bar&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.000&quot; MPa&quot;"/>
-    <numFmt numFmtId="177" formatCode="0.0%"/>
-    <numFmt numFmtId="178" formatCode="0.000&quot; mm&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.000000"/>
-    <numFmt numFmtId="180" formatCode="0.000&quot; kPa&quot;"/>
-    <numFmt numFmtId="181" formatCode="0.0000"/>
-    <numFmt numFmtId="182" formatCode="0.0"/>
+    <numFmt numFmtId="175" formatCode="0.###"/>
+    <numFmt numFmtId="176" formatCode="0.00&quot; bar&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.000&quot; MPa&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
+    <numFmt numFmtId="179" formatCode="0.000&quot; mm&quot;"/>
+    <numFmt numFmtId="180" formatCode="0.000000"/>
+    <numFmt numFmtId="181" formatCode="0.000&quot; kPa&quot;"/>
+    <numFmt numFmtId="182" formatCode="0.0000"/>
+    <numFmt numFmtId="183" formatCode="0.0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2943,6 +2944,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF1A1C1B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF1A1C1B"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -3177,11 +3184,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3189,7 +3196,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3197,11 +3204,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="179" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="180" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3217,7 +3224,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="181" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3225,19 +3232,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="182" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="180" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="182" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="183" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3245,7 +3252,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3535,11 +3542,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="37334958"/>
-        <c:axId val="31883330"/>
+        <c:axId val="20432413"/>
+        <c:axId val="94732094"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="37334958"/>
+        <c:axId val="20432413"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3572,14 +3579,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31883330"/>
+        <c:crossAx val="94732094"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31883330"/>
+        <c:axId val="94732094"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3628,7 +3635,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.000&quot; bar&quot;;\-0.000&quot; bar&quot;;&quot;&quot;" sourceLinked="1"/>
+        <c:numFmt formatCode="0.###" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3641,21 +3648,21 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
+          <a:bodyPr rot="-2700000"/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr sz="900">
                 <a:solidFill>
                   <a:srgbClr val="1A1C1B"/>
                 </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37334958"/>
+        <c:crossAx val="20432413"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
